--- a/local/agegroups/USAW.xlsx
+++ b/local/agegroups/USAW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/Misc/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F360DC8F-6BD5-A443-AA63-A862E68B9DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F80045-DCD9-474F-836A-74423CE465F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="500" windowWidth="39500" windowHeight="25100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26060" yWindow="1360" windowWidth="39500" windowHeight="25100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AgeGroups" sheetId="1" r:id="rId1"/>
@@ -766,34 +766,38 @@
       <c r="I2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
+        <v>30</v>
+      </c>
+      <c r="K2" s="2">
+        <v>33</v>
+      </c>
+      <c r="L2">
         <v>36</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>40</v>
       </c>
-      <c r="L2" s="1">
+      <c r="N2" s="1">
         <v>44</v>
       </c>
-      <c r="M2" s="1">
+      <c r="O2" s="1">
         <v>48</v>
       </c>
-      <c r="N2" s="1">
+      <c r="P2" s="1">
         <v>53</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>58</v>
       </c>
-      <c r="P2" s="1">
+      <c r="R2" s="1">
         <v>63</v>
       </c>
-      <c r="Q2" s="1">
-        <v>999</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
+      <c r="S2" s="1">
+        <v>999</v>
+      </c>
+      <c r="T2" s="1"/>
+      <c r="U2"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -824,34 +828,38 @@
       <c r="I3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
+        <v>30</v>
+      </c>
+      <c r="K3" s="2">
+        <v>33</v>
+      </c>
+      <c r="L3">
         <v>36</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>40</v>
       </c>
-      <c r="L3" s="1">
+      <c r="N3" s="1">
         <v>44</v>
       </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>48</v>
       </c>
-      <c r="N3" s="1">
+      <c r="P3" s="1">
         <v>53</v>
       </c>
-      <c r="O3" s="1">
+      <c r="Q3" s="1">
         <v>58</v>
       </c>
-      <c r="P3" s="1">
+      <c r="R3" s="1">
         <v>63</v>
       </c>
-      <c r="Q3" s="1">
-        <v>999</v>
-      </c>
-      <c r="R3" s="1"/>
-      <c r="S3"/>
+      <c r="S3" s="1">
+        <v>999</v>
+      </c>
       <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
+      <c r="U3"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
@@ -883,34 +891,32 @@
       <c r="I4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J4"/>
-      <c r="K4">
+      <c r="L4"/>
+      <c r="M4">
         <v>40</v>
       </c>
-      <c r="L4" s="1">
+      <c r="N4" s="1">
         <v>44</v>
       </c>
-      <c r="M4" s="1">
+      <c r="O4" s="1">
         <v>48</v>
       </c>
-      <c r="N4" s="1">
+      <c r="P4" s="1">
         <v>53</v>
       </c>
-      <c r="O4" s="1">
+      <c r="Q4" s="1">
         <v>58</v>
       </c>
-      <c r="P4" s="1">
+      <c r="R4" s="1">
         <v>63</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="S4" s="1">
         <v>69</v>
       </c>
-      <c r="R4" s="1">
-        <v>999</v>
-      </c>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4"/>
+      <c r="T4" s="1">
+        <v>999</v>
+      </c>
+      <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -942,34 +948,32 @@
       <c r="I5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5" s="1">
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5" s="1">
         <v>44</v>
       </c>
-      <c r="M5" s="1">
+      <c r="O5" s="1">
         <v>48</v>
       </c>
-      <c r="N5" s="1">
+      <c r="P5" s="1">
         <v>53</v>
       </c>
-      <c r="O5" s="1">
+      <c r="Q5" s="1">
         <v>58</v>
       </c>
-      <c r="P5" s="1">
+      <c r="R5" s="1">
         <v>63</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="S5" s="1">
         <v>69</v>
       </c>
-      <c r="R5" s="1">
+      <c r="T5" s="1">
         <v>77</v>
       </c>
-      <c r="S5" s="1">
-        <v>999</v>
-      </c>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
+      <c r="U5" s="1">
+        <v>999</v>
+      </c>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
@@ -1001,34 +1005,38 @@
       <c r="I6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
+        <v>30</v>
+      </c>
+      <c r="K6" s="2">
+        <v>33</v>
+      </c>
+      <c r="L6">
         <v>36</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>40</v>
       </c>
-      <c r="L6" s="1">
+      <c r="N6" s="1">
         <v>44</v>
       </c>
-      <c r="M6" s="1">
+      <c r="O6" s="1">
         <v>48</v>
       </c>
-      <c r="N6" s="1">
+      <c r="P6" s="1">
         <v>53</v>
       </c>
-      <c r="O6" s="1">
+      <c r="Q6" s="1">
         <v>58</v>
       </c>
-      <c r="P6" s="1">
+      <c r="R6" s="1">
         <v>63</v>
       </c>
-      <c r="Q6" s="1">
-        <v>999</v>
-      </c>
-      <c r="R6" s="1"/>
-      <c r="S6"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
+      <c r="S6" s="1">
+        <v>999</v>
+      </c>
+      <c r="T6" s="1"/>
+      <c r="U6"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -1059,34 +1067,38 @@
       <c r="I7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
+        <v>30</v>
+      </c>
+      <c r="K7" s="2">
+        <v>33</v>
+      </c>
+      <c r="L7">
         <v>36</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>40</v>
       </c>
-      <c r="L7" s="1">
+      <c r="N7" s="1">
         <v>44</v>
       </c>
-      <c r="M7" s="1">
+      <c r="O7" s="1">
         <v>48</v>
       </c>
-      <c r="N7" s="1">
+      <c r="P7" s="1">
         <v>53</v>
       </c>
-      <c r="O7" s="1">
+      <c r="Q7" s="1">
         <v>58</v>
       </c>
-      <c r="P7" s="1">
+      <c r="R7" s="1">
         <v>63</v>
       </c>
-      <c r="Q7" s="1">
-        <v>999</v>
-      </c>
-      <c r="R7" s="1"/>
-      <c r="S7"/>
+      <c r="S7" s="1">
+        <v>999</v>
+      </c>
       <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
+      <c r="U7"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
@@ -1118,34 +1130,32 @@
       <c r="I8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J8"/>
-      <c r="K8">
+      <c r="L8"/>
+      <c r="M8">
         <v>40</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>44</v>
       </c>
-      <c r="M8" s="1">
+      <c r="O8" s="1">
         <v>48</v>
       </c>
-      <c r="N8" s="1">
+      <c r="P8" s="1">
         <v>53</v>
       </c>
-      <c r="O8" s="1">
+      <c r="Q8" s="1">
         <v>58</v>
       </c>
-      <c r="P8" s="1">
+      <c r="R8" s="1">
         <v>63</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="S8" s="1">
         <v>69</v>
       </c>
-      <c r="R8" s="1">
-        <v>999</v>
-      </c>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8"/>
+      <c r="T8" s="1">
+        <v>999</v>
+      </c>
+      <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
@@ -1177,34 +1187,32 @@
       <c r="I9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9" s="1">
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9" s="1">
         <v>44</v>
       </c>
-      <c r="M9" s="1">
+      <c r="O9" s="1">
         <v>48</v>
       </c>
-      <c r="N9" s="1">
+      <c r="P9" s="1">
         <v>53</v>
       </c>
-      <c r="O9" s="1">
+      <c r="Q9" s="1">
         <v>58</v>
       </c>
-      <c r="P9" s="1">
+      <c r="R9" s="1">
         <v>63</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="S9" s="1">
         <v>69</v>
       </c>
-      <c r="R9" s="1">
+      <c r="T9" s="1">
         <v>77</v>
       </c>
-      <c r="S9" s="1">
-        <v>999</v>
-      </c>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
+      <c r="U9" s="1">
+        <v>999</v>
+      </c>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
@@ -1237,33 +1245,31 @@
       <c r="I10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="M10" s="1">
+      <c r="L10" s="1"/>
+      <c r="O10" s="1">
         <v>48</v>
       </c>
-      <c r="N10" s="1">
+      <c r="P10" s="1">
         <v>53</v>
       </c>
-      <c r="O10" s="1">
+      <c r="Q10" s="1">
         <v>58</v>
       </c>
-      <c r="P10" s="1">
+      <c r="R10" s="1">
         <v>63</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="S10" s="1">
         <v>69</v>
       </c>
-      <c r="R10" s="1">
+      <c r="T10" s="1">
         <v>77</v>
       </c>
-      <c r="S10" s="1">
+      <c r="U10" s="1">
         <v>86</v>
       </c>
-      <c r="T10" s="1">
-        <v>999</v>
-      </c>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
+      <c r="V10" s="1">
+        <v>999</v>
+      </c>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
@@ -1295,33 +1301,31 @@
       <c r="I11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="M11" s="1">
+      <c r="L11" s="1"/>
+      <c r="O11" s="1">
         <v>48</v>
       </c>
-      <c r="N11" s="1">
+      <c r="P11" s="1">
         <v>53</v>
       </c>
-      <c r="O11" s="1">
+      <c r="Q11" s="1">
         <v>58</v>
       </c>
-      <c r="P11" s="1">
+      <c r="R11" s="1">
         <v>63</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="S11" s="1">
         <v>69</v>
       </c>
-      <c r="R11" s="1">
+      <c r="T11" s="1">
         <v>77</v>
       </c>
-      <c r="S11" s="1">
+      <c r="U11" s="1">
         <v>86</v>
       </c>
-      <c r="T11" s="1">
-        <v>999</v>
-      </c>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
+      <c r="V11" s="1">
+        <v>999</v>
+      </c>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
@@ -1352,35 +1356,33 @@
       <c r="I12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1">
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1">
         <v>48</v>
       </c>
-      <c r="N12" s="1">
+      <c r="P12" s="1">
         <v>53</v>
       </c>
-      <c r="O12" s="1">
+      <c r="Q12" s="1">
         <v>58</v>
       </c>
-      <c r="P12" s="1">
+      <c r="R12" s="1">
         <v>63</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="S12" s="1">
         <v>69</v>
       </c>
-      <c r="R12" s="1">
+      <c r="T12" s="1">
         <v>77</v>
       </c>
-      <c r="S12" s="1">
+      <c r="U12" s="1">
         <v>86</v>
       </c>
-      <c r="T12" s="1">
-        <v>999</v>
-      </c>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
+      <c r="V12" s="1">
+        <v>999</v>
+      </c>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -1412,33 +1414,31 @@
       <c r="I13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="M13" s="1">
+      <c r="L13" s="1"/>
+      <c r="O13" s="1">
         <v>48</v>
       </c>
-      <c r="N13" s="1">
+      <c r="P13" s="1">
         <v>53</v>
       </c>
-      <c r="O13" s="1">
+      <c r="Q13" s="1">
         <v>58</v>
       </c>
-      <c r="P13" s="1">
+      <c r="R13" s="1">
         <v>63</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="S13" s="1">
         <v>69</v>
       </c>
-      <c r="R13" s="1">
+      <c r="T13" s="1">
         <v>77</v>
       </c>
-      <c r="S13" s="1">
+      <c r="U13" s="1">
         <v>86</v>
       </c>
-      <c r="T13" s="1">
-        <v>999</v>
-      </c>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
+      <c r="V13" s="1">
+        <v>999</v>
+      </c>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
@@ -1470,33 +1470,31 @@
       <c r="I14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="M14" s="1">
+      <c r="L14" s="1"/>
+      <c r="O14" s="1">
         <v>48</v>
       </c>
-      <c r="N14" s="1">
+      <c r="P14" s="1">
         <v>53</v>
       </c>
-      <c r="O14" s="1">
+      <c r="Q14" s="1">
         <v>58</v>
       </c>
-      <c r="P14" s="1">
+      <c r="R14" s="1">
         <v>63</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="S14" s="1">
         <v>69</v>
       </c>
-      <c r="R14" s="1">
+      <c r="T14" s="1">
         <v>77</v>
       </c>
-      <c r="S14" s="1">
+      <c r="U14" s="1">
         <v>86</v>
       </c>
-      <c r="T14" s="1">
-        <v>999</v>
-      </c>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
+      <c r="V14" s="1">
+        <v>999</v>
+      </c>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -1527,35 +1525,33 @@
       <c r="I15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1">
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1">
         <v>48</v>
       </c>
-      <c r="N15" s="1">
+      <c r="P15" s="1">
         <v>53</v>
       </c>
-      <c r="O15" s="1">
+      <c r="Q15" s="1">
         <v>58</v>
       </c>
-      <c r="P15" s="1">
+      <c r="R15" s="1">
         <v>63</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="S15" s="1">
         <v>69</v>
       </c>
-      <c r="R15" s="1">
+      <c r="T15" s="1">
         <v>77</v>
       </c>
-      <c r="S15" s="1">
+      <c r="U15" s="1">
         <v>86</v>
       </c>
-      <c r="T15" s="1">
-        <v>999</v>
-      </c>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
+      <c r="V15" s="1">
+        <v>999</v>
+      </c>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -1586,35 +1582,33 @@
       <c r="I16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1">
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1">
         <v>48</v>
       </c>
-      <c r="N16" s="1">
+      <c r="P16" s="1">
         <v>53</v>
       </c>
-      <c r="O16" s="1">
+      <c r="Q16" s="1">
         <v>58</v>
       </c>
-      <c r="P16" s="1">
+      <c r="R16" s="1">
         <v>63</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="S16" s="1">
         <v>69</v>
       </c>
-      <c r="R16" s="1">
+      <c r="T16" s="1">
         <v>77</v>
       </c>
-      <c r="S16" s="1">
+      <c r="U16" s="1">
         <v>86</v>
       </c>
-      <c r="T16" s="1">
-        <v>999</v>
-      </c>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
+      <c r="V16" s="1">
+        <v>999</v>
+      </c>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
@@ -1646,33 +1640,31 @@
       <c r="I17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="M17" s="1">
+      <c r="L17" s="1"/>
+      <c r="O17" s="1">
         <v>48</v>
       </c>
-      <c r="N17" s="1">
+      <c r="P17" s="1">
         <v>53</v>
       </c>
-      <c r="O17" s="1">
+      <c r="Q17" s="1">
         <v>58</v>
       </c>
-      <c r="P17" s="1">
+      <c r="R17" s="1">
         <v>63</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="S17" s="1">
         <v>69</v>
       </c>
-      <c r="R17" s="1">
+      <c r="T17" s="1">
         <v>77</v>
       </c>
-      <c r="S17" s="1">
+      <c r="U17" s="1">
         <v>86</v>
       </c>
-      <c r="T17" s="1">
-        <v>999</v>
-      </c>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
+      <c r="V17" s="1">
+        <v>999</v>
+      </c>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -1703,35 +1695,33 @@
       <c r="I18" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J18"/>
-      <c r="K18"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1">
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
         <v>48</v>
       </c>
-      <c r="N18" s="1">
+      <c r="P18" s="1">
         <v>53</v>
       </c>
-      <c r="O18" s="1">
+      <c r="Q18" s="1">
         <v>58</v>
       </c>
-      <c r="P18" s="1">
+      <c r="R18" s="1">
         <v>63</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="S18" s="1">
         <v>69</v>
       </c>
-      <c r="R18" s="1">
+      <c r="T18" s="1">
         <v>77</v>
       </c>
-      <c r="S18" s="1">
+      <c r="U18" s="1">
         <v>86</v>
       </c>
-      <c r="T18" s="1">
-        <v>999</v>
-      </c>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
+      <c r="V18" s="1">
+        <v>999</v>
+      </c>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
@@ -1762,35 +1752,33 @@
       <c r="I19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1">
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
         <v>48</v>
       </c>
-      <c r="N19" s="1">
+      <c r="P19" s="1">
         <v>53</v>
       </c>
-      <c r="O19" s="1">
+      <c r="Q19" s="1">
         <v>58</v>
       </c>
-      <c r="P19" s="1">
+      <c r="R19" s="1">
         <v>63</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="S19" s="1">
         <v>69</v>
       </c>
-      <c r="R19" s="1">
+      <c r="T19" s="1">
         <v>77</v>
       </c>
-      <c r="S19" s="1">
+      <c r="U19" s="1">
         <v>86</v>
       </c>
-      <c r="T19" s="1">
-        <v>999</v>
-      </c>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
+      <c r="V19" s="1">
+        <v>999</v>
+      </c>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
@@ -1821,35 +1809,33 @@
       <c r="I20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1">
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1">
         <v>48</v>
       </c>
-      <c r="N20" s="1">
+      <c r="P20" s="1">
         <v>53</v>
       </c>
-      <c r="O20" s="1">
+      <c r="Q20" s="1">
         <v>58</v>
       </c>
-      <c r="P20" s="1">
+      <c r="R20" s="1">
         <v>63</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="S20" s="1">
         <v>69</v>
       </c>
-      <c r="R20" s="1">
+      <c r="T20" s="1">
         <v>77</v>
       </c>
-      <c r="S20" s="1">
+      <c r="U20" s="1">
         <v>86</v>
       </c>
-      <c r="T20" s="1">
-        <v>999</v>
-      </c>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
+      <c r="V20" s="1">
+        <v>999</v>
+      </c>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
@@ -1880,35 +1866,33 @@
       <c r="I21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1">
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
         <v>48</v>
       </c>
-      <c r="N21" s="1">
+      <c r="P21" s="1">
         <v>53</v>
       </c>
-      <c r="O21" s="1">
+      <c r="Q21" s="1">
         <v>58</v>
       </c>
-      <c r="P21" s="1">
+      <c r="R21" s="1">
         <v>63</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="S21" s="1">
         <v>69</v>
       </c>
-      <c r="R21" s="1">
+      <c r="T21" s="1">
         <v>77</v>
       </c>
-      <c r="S21" s="1">
+      <c r="U21" s="1">
         <v>86</v>
       </c>
-      <c r="T21" s="1">
-        <v>999</v>
-      </c>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
+      <c r="V21" s="1">
+        <v>999</v>
+      </c>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
@@ -1939,35 +1923,33 @@
       <c r="I22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1">
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
         <v>48</v>
       </c>
-      <c r="N22" s="1">
+      <c r="P22" s="1">
         <v>53</v>
       </c>
-      <c r="O22" s="1">
+      <c r="Q22" s="1">
         <v>58</v>
       </c>
-      <c r="P22" s="1">
+      <c r="R22" s="1">
         <v>63</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="S22" s="1">
         <v>69</v>
       </c>
-      <c r="R22" s="1">
+      <c r="T22" s="1">
         <v>77</v>
       </c>
-      <c r="S22" s="1">
+      <c r="U22" s="1">
         <v>86</v>
       </c>
-      <c r="T22" s="1">
-        <v>999</v>
-      </c>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
+      <c r="V22" s="1">
+        <v>999</v>
+      </c>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
@@ -1998,35 +1980,33 @@
       <c r="I23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1">
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1">
         <v>48</v>
       </c>
-      <c r="N23" s="1">
+      <c r="P23" s="1">
         <v>53</v>
       </c>
-      <c r="O23" s="1">
+      <c r="Q23" s="1">
         <v>58</v>
       </c>
-      <c r="P23" s="1">
+      <c r="R23" s="1">
         <v>63</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="S23" s="1">
         <v>69</v>
       </c>
-      <c r="R23" s="1">
+      <c r="T23" s="1">
         <v>77</v>
       </c>
-      <c r="S23" s="1">
+      <c r="U23" s="1">
         <v>86</v>
       </c>
-      <c r="T23" s="1">
-        <v>999</v>
-      </c>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
+      <c r="V23" s="1">
+        <v>999</v>
+      </c>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -2057,35 +2037,33 @@
       <c r="I24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1">
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
         <v>48</v>
       </c>
-      <c r="N24" s="1">
+      <c r="P24" s="1">
         <v>53</v>
       </c>
-      <c r="O24" s="1">
+      <c r="Q24" s="1">
         <v>58</v>
       </c>
-      <c r="P24" s="1">
+      <c r="R24" s="1">
         <v>63</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="S24" s="1">
         <v>69</v>
       </c>
-      <c r="R24" s="1">
+      <c r="T24" s="1">
         <v>77</v>
       </c>
-      <c r="S24" s="1">
+      <c r="U24" s="1">
         <v>86</v>
       </c>
-      <c r="T24" s="1">
-        <v>999</v>
-      </c>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
+      <c r="V24" s="1">
+        <v>999</v>
+      </c>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
@@ -2116,35 +2094,33 @@
       <c r="I25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1">
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
         <v>48</v>
       </c>
-      <c r="N25" s="1">
+      <c r="P25" s="1">
         <v>53</v>
       </c>
-      <c r="O25" s="1">
+      <c r="Q25" s="1">
         <v>58</v>
       </c>
-      <c r="P25" s="1">
+      <c r="R25" s="1">
         <v>63</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="S25" s="1">
         <v>69</v>
       </c>
-      <c r="R25" s="1">
+      <c r="T25" s="1">
         <v>77</v>
       </c>
-      <c r="S25" s="1">
+      <c r="U25" s="1">
         <v>86</v>
       </c>
-      <c r="T25" s="1">
-        <v>999</v>
-      </c>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
+      <c r="V25" s="1">
+        <v>999</v>
+      </c>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
@@ -2175,35 +2151,33 @@
       <c r="I26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1">
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
         <v>48</v>
       </c>
-      <c r="N26" s="1">
+      <c r="P26" s="1">
         <v>53</v>
       </c>
-      <c r="O26" s="1">
+      <c r="Q26" s="1">
         <v>58</v>
       </c>
-      <c r="P26" s="1">
+      <c r="R26" s="1">
         <v>63</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="S26" s="1">
         <v>69</v>
       </c>
-      <c r="R26" s="1">
+      <c r="T26" s="1">
         <v>77</v>
       </c>
-      <c r="S26" s="1">
+      <c r="U26" s="1">
         <v>86</v>
       </c>
-      <c r="T26" s="1">
-        <v>999</v>
-      </c>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
+      <c r="V26" s="1">
+        <v>999</v>
+      </c>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
@@ -2234,35 +2208,33 @@
       <c r="I27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1">
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1">
         <v>48</v>
       </c>
-      <c r="N27" s="1">
+      <c r="P27" s="1">
         <v>53</v>
       </c>
-      <c r="O27" s="1">
+      <c r="Q27" s="1">
         <v>58</v>
       </c>
-      <c r="P27" s="1">
+      <c r="R27" s="1">
         <v>63</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="S27" s="1">
         <v>69</v>
       </c>
-      <c r="R27" s="1">
+      <c r="T27" s="1">
         <v>77</v>
       </c>
-      <c r="S27" s="1">
+      <c r="U27" s="1">
         <v>86</v>
       </c>
-      <c r="T27" s="1">
-        <v>999</v>
-      </c>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
+      <c r="V27" s="1">
+        <v>999</v>
+      </c>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
@@ -2293,35 +2265,33 @@
       <c r="I28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1">
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1">
         <v>48</v>
       </c>
-      <c r="N28" s="1">
+      <c r="P28" s="1">
         <v>53</v>
       </c>
-      <c r="O28" s="1">
+      <c r="Q28" s="1">
         <v>58</v>
       </c>
-      <c r="P28" s="1">
+      <c r="R28" s="1">
         <v>63</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="S28" s="1">
         <v>69</v>
       </c>
-      <c r="R28" s="1">
+      <c r="T28" s="1">
         <v>77</v>
       </c>
-      <c r="S28" s="1">
+      <c r="U28" s="1">
         <v>86</v>
       </c>
-      <c r="T28" s="1">
-        <v>999</v>
-      </c>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
+      <c r="V28" s="1">
+        <v>999</v>
+      </c>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
@@ -2352,35 +2322,33 @@
       <c r="I29" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1">
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1">
         <v>48</v>
       </c>
-      <c r="N29" s="1">
+      <c r="P29" s="1">
         <v>53</v>
       </c>
-      <c r="O29" s="1">
+      <c r="Q29" s="1">
         <v>58</v>
       </c>
-      <c r="P29" s="1">
+      <c r="R29" s="1">
         <v>63</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="S29" s="1">
         <v>69</v>
       </c>
-      <c r="R29" s="1">
+      <c r="T29" s="1">
         <v>77</v>
       </c>
-      <c r="S29" s="1">
+      <c r="U29" s="1">
         <v>86</v>
       </c>
-      <c r="T29" s="1">
-        <v>999</v>
-      </c>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
+      <c r="V29" s="1">
+        <v>999</v>
+      </c>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
@@ -2411,35 +2379,33 @@
       <c r="I30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1">
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1">
         <v>48</v>
       </c>
-      <c r="N30" s="1">
+      <c r="P30" s="1">
         <v>53</v>
       </c>
-      <c r="O30" s="1">
+      <c r="Q30" s="1">
         <v>58</v>
       </c>
-      <c r="P30" s="1">
+      <c r="R30" s="1">
         <v>63</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="S30" s="1">
         <v>69</v>
       </c>
-      <c r="R30" s="1">
+      <c r="T30" s="1">
         <v>77</v>
       </c>
-      <c r="S30" s="1">
+      <c r="U30" s="1">
         <v>86</v>
       </c>
-      <c r="T30" s="1">
-        <v>999</v>
-      </c>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
+      <c r="V30" s="1">
+        <v>999</v>
+      </c>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
@@ -2470,35 +2436,33 @@
       <c r="I31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1">
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1">
         <v>48</v>
       </c>
-      <c r="N31" s="1">
+      <c r="P31" s="1">
         <v>53</v>
       </c>
-      <c r="O31" s="1">
+      <c r="Q31" s="1">
         <v>58</v>
       </c>
-      <c r="P31" s="1">
+      <c r="R31" s="1">
         <v>63</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="S31" s="1">
         <v>69</v>
       </c>
-      <c r="R31" s="1">
+      <c r="T31" s="1">
         <v>77</v>
       </c>
-      <c r="S31" s="1">
+      <c r="U31" s="1">
         <v>86</v>
       </c>
-      <c r="T31" s="1">
-        <v>999</v>
-      </c>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
+      <c r="V31" s="1">
+        <v>999</v>
+      </c>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
@@ -2529,35 +2493,33 @@
       <c r="I32" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1">
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1">
         <v>48</v>
       </c>
-      <c r="N32" s="1">
+      <c r="P32" s="1">
         <v>53</v>
       </c>
-      <c r="O32" s="1">
+      <c r="Q32" s="1">
         <v>58</v>
       </c>
-      <c r="P32" s="1">
+      <c r="R32" s="1">
         <v>63</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="S32" s="1">
         <v>69</v>
       </c>
-      <c r="R32" s="1">
+      <c r="T32" s="1">
         <v>77</v>
       </c>
-      <c r="S32" s="1">
+      <c r="U32" s="1">
         <v>86</v>
       </c>
-      <c r="T32" s="1">
-        <v>999</v>
-      </c>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
+      <c r="V32" s="1">
+        <v>999</v>
+      </c>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -2588,35 +2550,33 @@
       <c r="I33" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1">
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1">
         <v>48</v>
       </c>
-      <c r="N33" s="1">
+      <c r="P33" s="1">
         <v>53</v>
       </c>
-      <c r="O33" s="1">
+      <c r="Q33" s="1">
         <v>58</v>
       </c>
-      <c r="P33" s="1">
+      <c r="R33" s="1">
         <v>63</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="S33" s="1">
         <v>69</v>
       </c>
-      <c r="R33" s="1">
+      <c r="T33" s="1">
         <v>77</v>
       </c>
-      <c r="S33" s="1">
+      <c r="U33" s="1">
         <v>86</v>
       </c>
-      <c r="T33" s="1">
-        <v>999</v>
-      </c>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
+      <c r="V33" s="1">
+        <v>999</v>
+      </c>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
@@ -2647,35 +2607,33 @@
       <c r="I34" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1">
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1">
         <v>48</v>
       </c>
-      <c r="N34" s="1">
+      <c r="P34" s="1">
         <v>53</v>
       </c>
-      <c r="O34" s="1">
+      <c r="Q34" s="1">
         <v>58</v>
       </c>
-      <c r="P34" s="1">
+      <c r="R34" s="1">
         <v>63</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="S34" s="1">
         <v>69</v>
       </c>
-      <c r="R34" s="1">
+      <c r="T34" s="1">
         <v>77</v>
       </c>
-      <c r="S34" s="1">
+      <c r="U34" s="1">
         <v>86</v>
       </c>
-      <c r="T34" s="1">
-        <v>999</v>
-      </c>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
+      <c r="V34" s="1">
+        <v>999</v>
+      </c>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
@@ -2706,35 +2664,33 @@
       <c r="I35" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1">
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1">
         <v>48</v>
       </c>
-      <c r="N35" s="1">
+      <c r="P35" s="1">
         <v>53</v>
       </c>
-      <c r="O35" s="1">
+      <c r="Q35" s="1">
         <v>58</v>
       </c>
-      <c r="P35" s="1">
+      <c r="R35" s="1">
         <v>63</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="S35" s="1">
         <v>69</v>
       </c>
-      <c r="R35" s="1">
+      <c r="T35" s="1">
         <v>77</v>
       </c>
-      <c r="S35" s="1">
+      <c r="U35" s="1">
         <v>86</v>
       </c>
-      <c r="T35" s="1">
-        <v>999</v>
-      </c>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
+      <c r="V35" s="1">
+        <v>999</v>
+      </c>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
@@ -2765,35 +2721,33 @@
       <c r="I36" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1">
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1">
         <v>48</v>
       </c>
-      <c r="N36" s="1">
+      <c r="P36" s="1">
         <v>53</v>
       </c>
-      <c r="O36" s="1">
+      <c r="Q36" s="1">
         <v>58</v>
       </c>
-      <c r="P36" s="1">
+      <c r="R36" s="1">
         <v>63</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="S36" s="1">
         <v>69</v>
       </c>
-      <c r="R36" s="1">
+      <c r="T36" s="1">
         <v>77</v>
       </c>
-      <c r="S36" s="1">
+      <c r="U36" s="1">
         <v>86</v>
       </c>
-      <c r="T36" s="1">
-        <v>999</v>
-      </c>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
+      <c r="V36" s="1">
+        <v>999</v>
+      </c>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -2824,35 +2778,33 @@
       <c r="I37" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1">
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1">
         <v>48</v>
       </c>
-      <c r="N37" s="1">
+      <c r="P37" s="1">
         <v>53</v>
       </c>
-      <c r="O37" s="1">
+      <c r="Q37" s="1">
         <v>58</v>
       </c>
-      <c r="P37" s="1">
+      <c r="R37" s="1">
         <v>63</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="S37" s="1">
         <v>69</v>
       </c>
-      <c r="R37" s="1">
+      <c r="T37" s="1">
         <v>77</v>
       </c>
-      <c r="S37" s="1">
+      <c r="U37" s="1">
         <v>86</v>
       </c>
-      <c r="T37" s="1">
-        <v>999</v>
-      </c>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
+      <c r="V37" s="1">
+        <v>999</v>
+      </c>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
@@ -2883,35 +2835,33 @@
       <c r="I38" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J38"/>
-      <c r="K38"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1">
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1">
         <v>48</v>
       </c>
-      <c r="N38" s="1">
+      <c r="P38" s="1">
         <v>53</v>
       </c>
-      <c r="O38" s="1">
+      <c r="Q38" s="1">
         <v>58</v>
       </c>
-      <c r="P38" s="1">
+      <c r="R38" s="1">
         <v>63</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="S38" s="1">
         <v>69</v>
       </c>
-      <c r="R38" s="1">
+      <c r="T38" s="1">
         <v>77</v>
       </c>
-      <c r="S38" s="1">
+      <c r="U38" s="1">
         <v>86</v>
       </c>
-      <c r="T38" s="1">
-        <v>999</v>
-      </c>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
+      <c r="V38" s="1">
+        <v>999</v>
+      </c>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
@@ -2942,35 +2892,33 @@
       <c r="I39" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J39"/>
-      <c r="K39"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1">
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1">
         <v>48</v>
       </c>
-      <c r="N39" s="1">
+      <c r="P39" s="1">
         <v>53</v>
       </c>
-      <c r="O39" s="1">
+      <c r="Q39" s="1">
         <v>58</v>
       </c>
-      <c r="P39" s="1">
+      <c r="R39" s="1">
         <v>63</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="S39" s="1">
         <v>69</v>
       </c>
-      <c r="R39" s="1">
+      <c r="T39" s="1">
         <v>77</v>
       </c>
-      <c r="S39" s="1">
+      <c r="U39" s="1">
         <v>86</v>
       </c>
-      <c r="T39" s="1">
-        <v>999</v>
-      </c>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
+      <c r="V39" s="1">
+        <v>999</v>
+      </c>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
@@ -3001,35 +2949,33 @@
       <c r="I40" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J40"/>
-      <c r="K40"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1">
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1">
         <v>48</v>
       </c>
-      <c r="N40" s="1">
+      <c r="P40" s="1">
         <v>53</v>
       </c>
-      <c r="O40" s="1">
+      <c r="Q40" s="1">
         <v>58</v>
       </c>
-      <c r="P40" s="1">
+      <c r="R40" s="1">
         <v>63</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="S40" s="1">
         <v>69</v>
       </c>
-      <c r="R40" s="1">
+      <c r="T40" s="1">
         <v>77</v>
       </c>
-      <c r="S40" s="1">
+      <c r="U40" s="1">
         <v>86</v>
       </c>
-      <c r="T40" s="1">
-        <v>999</v>
-      </c>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
+      <c r="V40" s="1">
+        <v>999</v>
+      </c>
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
@@ -3060,35 +3006,33 @@
       <c r="I41" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J41"/>
-      <c r="K41"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1">
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1">
         <v>48</v>
       </c>
-      <c r="N41" s="1">
+      <c r="P41" s="1">
         <v>53</v>
       </c>
-      <c r="O41" s="1">
+      <c r="Q41" s="1">
         <v>58</v>
       </c>
-      <c r="P41" s="1">
+      <c r="R41" s="1">
         <v>63</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="S41" s="1">
         <v>69</v>
       </c>
-      <c r="R41" s="1">
+      <c r="T41" s="1">
         <v>77</v>
       </c>
-      <c r="S41" s="1">
+      <c r="U41" s="1">
         <v>86</v>
       </c>
-      <c r="T41" s="1">
-        <v>999</v>
-      </c>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
+      <c r="V41" s="1">
+        <v>999</v>
+      </c>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
@@ -3119,35 +3063,33 @@
       <c r="I42" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1">
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1">
         <v>48</v>
       </c>
-      <c r="N42" s="1">
+      <c r="P42" s="1">
         <v>53</v>
       </c>
-      <c r="O42" s="1">
+      <c r="Q42" s="1">
         <v>58</v>
       </c>
-      <c r="P42" s="1">
+      <c r="R42" s="1">
         <v>63</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="S42" s="1">
         <v>69</v>
       </c>
-      <c r="R42" s="1">
+      <c r="T42" s="1">
         <v>77</v>
       </c>
-      <c r="S42" s="1">
+      <c r="U42" s="1">
         <v>86</v>
       </c>
-      <c r="T42" s="1">
-        <v>999</v>
-      </c>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
+      <c r="V42" s="1">
+        <v>999</v>
+      </c>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -3178,35 +3120,33 @@
       <c r="I43" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1">
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1">
         <v>48</v>
       </c>
-      <c r="N43" s="1">
+      <c r="P43" s="1">
         <v>53</v>
       </c>
-      <c r="O43" s="1">
+      <c r="Q43" s="1">
         <v>58</v>
       </c>
-      <c r="P43" s="1">
+      <c r="R43" s="1">
         <v>63</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="S43" s="1">
         <v>69</v>
       </c>
-      <c r="R43" s="1">
+      <c r="T43" s="1">
         <v>77</v>
       </c>
-      <c r="S43" s="1">
+      <c r="U43" s="1">
         <v>86</v>
       </c>
-      <c r="T43" s="1">
-        <v>999</v>
-      </c>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
+      <c r="V43" s="1">
+        <v>999</v>
+      </c>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -3237,35 +3177,33 @@
       <c r="I44" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J44"/>
-      <c r="K44"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1">
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1">
         <v>48</v>
       </c>
-      <c r="N44" s="1">
+      <c r="P44" s="1">
         <v>53</v>
       </c>
-      <c r="O44" s="1">
+      <c r="Q44" s="1">
         <v>58</v>
       </c>
-      <c r="P44" s="1">
+      <c r="R44" s="1">
         <v>63</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="S44" s="1">
         <v>69</v>
       </c>
-      <c r="R44" s="1">
+      <c r="T44" s="1">
         <v>77</v>
       </c>
-      <c r="S44" s="1">
+      <c r="U44" s="1">
         <v>86</v>
       </c>
-      <c r="T44" s="1">
-        <v>999</v>
-      </c>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
+      <c r="V44" s="1">
+        <v>999</v>
+      </c>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -3296,35 +3234,33 @@
       <c r="I45" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1">
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1">
         <v>48</v>
       </c>
-      <c r="N45" s="1">
+      <c r="P45" s="1">
         <v>53</v>
       </c>
-      <c r="O45" s="1">
+      <c r="Q45" s="1">
         <v>58</v>
       </c>
-      <c r="P45" s="1">
+      <c r="R45" s="1">
         <v>63</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="S45" s="1">
         <v>69</v>
       </c>
-      <c r="R45" s="1">
+      <c r="T45" s="1">
         <v>77</v>
       </c>
-      <c r="S45" s="1">
+      <c r="U45" s="1">
         <v>86</v>
       </c>
-      <c r="T45" s="1">
-        <v>999</v>
-      </c>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
+      <c r="V45" s="1">
+        <v>999</v>
+      </c>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
@@ -3358,19 +3294,17 @@
       <c r="I46" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
+      <c r="L46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="T46" s="1">
-        <v>999</v>
-      </c>
+      <c r="T46" s="1"/>
       <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
+      <c r="V46" s="1">
+        <v>999</v>
+      </c>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -3403,19 +3337,17 @@
       <c r="I47" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
+      <c r="L47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="T47" s="1">
-        <v>999</v>
-      </c>
+      <c r="T47" s="1"/>
       <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
+      <c r="V47" s="1">
+        <v>999</v>
+      </c>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -3446,32 +3378,36 @@
       <c r="I48" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="2">
+        <v>32</v>
+      </c>
+      <c r="K48" s="2">
+        <v>36</v>
+      </c>
+      <c r="L48" s="1">
         <v>40</v>
       </c>
-      <c r="K48">
+      <c r="M48">
         <v>44</v>
       </c>
-      <c r="L48">
+      <c r="N48">
         <v>48</v>
       </c>
-      <c r="M48" s="1">
+      <c r="O48" s="1">
         <v>52</v>
       </c>
-      <c r="N48" s="1">
+      <c r="P48" s="1">
         <v>56</v>
       </c>
-      <c r="O48" s="1">
-        <v>60</v>
-      </c>
-      <c r="P48" s="1">
+      <c r="Q48" s="1">
+        <v>60</v>
+      </c>
+      <c r="R48" s="1">
         <v>65</v>
       </c>
-      <c r="Q48" s="1">
-        <v>999</v>
-      </c>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
+      <c r="S48" s="1">
+        <v>999</v>
+      </c>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
@@ -3504,32 +3440,36 @@
       <c r="I49" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="2">
+        <v>32</v>
+      </c>
+      <c r="K49" s="2">
+        <v>36</v>
+      </c>
+      <c r="L49" s="1">
         <v>40</v>
       </c>
-      <c r="K49">
+      <c r="M49">
         <v>44</v>
       </c>
-      <c r="L49">
+      <c r="N49">
         <v>48</v>
       </c>
-      <c r="M49" s="1">
+      <c r="O49" s="1">
         <v>52</v>
       </c>
-      <c r="N49" s="1">
+      <c r="P49" s="1">
         <v>56</v>
       </c>
-      <c r="O49" s="1">
-        <v>60</v>
-      </c>
-      <c r="P49" s="1">
+      <c r="Q49" s="1">
+        <v>60</v>
+      </c>
+      <c r="R49" s="1">
         <v>65</v>
       </c>
-      <c r="Q49" s="1">
-        <v>999</v>
-      </c>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
+      <c r="S49" s="1">
+        <v>999</v>
+      </c>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
@@ -3562,34 +3502,32 @@
       <c r="I50" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J50" s="1"/>
-      <c r="K50"/>
-      <c r="L50">
+      <c r="L50" s="1"/>
+      <c r="M50"/>
+      <c r="N50">
         <v>48</v>
       </c>
-      <c r="M50" s="1">
+      <c r="O50" s="1">
         <v>52</v>
       </c>
-      <c r="N50" s="1">
+      <c r="P50" s="1">
         <v>56</v>
       </c>
-      <c r="O50" s="1">
-        <v>60</v>
-      </c>
-      <c r="P50" s="1">
+      <c r="Q50" s="1">
+        <v>60</v>
+      </c>
+      <c r="R50" s="1">
         <v>65</v>
       </c>
-      <c r="Q50" s="1">
+      <c r="S50" s="1">
         <v>71</v>
       </c>
-      <c r="R50" s="1">
+      <c r="T50" s="1">
         <v>79</v>
       </c>
-      <c r="S50" s="1">
-        <v>999</v>
-      </c>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
+      <c r="U50" s="1">
+        <v>999</v>
+      </c>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
@@ -3620,35 +3558,33 @@
       <c r="I51" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J51"/>
-      <c r="K51"/>
-      <c r="L51" s="1"/>
-      <c r="N51" s="1">
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51" s="1"/>
+      <c r="P51" s="1">
         <v>56</v>
       </c>
-      <c r="O51" s="1">
-        <v>60</v>
-      </c>
-      <c r="P51" s="1">
+      <c r="Q51" s="1">
+        <v>60</v>
+      </c>
+      <c r="R51" s="1">
         <v>65</v>
       </c>
-      <c r="Q51" s="1">
+      <c r="S51" s="1">
         <v>71</v>
       </c>
-      <c r="R51" s="1">
+      <c r="T51" s="1">
         <v>79</v>
       </c>
-      <c r="S51" s="1">
+      <c r="U51" s="1">
         <v>88</v>
       </c>
-      <c r="T51" s="1">
+      <c r="V51" s="1">
         <v>94</v>
       </c>
-      <c r="U51" s="1">
-        <v>999</v>
-      </c>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1"/>
+      <c r="W51" s="1">
+        <v>999</v>
+      </c>
       <c r="X51" s="1"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.2">
@@ -3677,32 +3613,36 @@
       <c r="I52" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="2">
+        <v>32</v>
+      </c>
+      <c r="K52" s="2">
+        <v>36</v>
+      </c>
+      <c r="L52" s="1">
         <v>40</v>
       </c>
-      <c r="K52">
+      <c r="M52">
         <v>44</v>
       </c>
-      <c r="L52">
+      <c r="N52">
         <v>48</v>
       </c>
-      <c r="M52" s="1">
+      <c r="O52" s="1">
         <v>52</v>
       </c>
-      <c r="N52" s="1">
+      <c r="P52" s="1">
         <v>56</v>
       </c>
-      <c r="O52" s="1">
-        <v>60</v>
-      </c>
-      <c r="P52" s="1">
+      <c r="Q52" s="1">
+        <v>60</v>
+      </c>
+      <c r="R52" s="1">
         <v>65</v>
       </c>
-      <c r="Q52" s="1">
-        <v>999</v>
-      </c>
-      <c r="R52" s="1"/>
-      <c r="S52" s="1"/>
+      <c r="S52" s="1">
+        <v>999</v>
+      </c>
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
@@ -3735,32 +3675,36 @@
       <c r="I53" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="2">
+        <v>32</v>
+      </c>
+      <c r="K53" s="2">
+        <v>36</v>
+      </c>
+      <c r="L53" s="1">
         <v>40</v>
       </c>
-      <c r="K53">
+      <c r="M53">
         <v>44</v>
       </c>
-      <c r="L53">
+      <c r="N53">
         <v>48</v>
       </c>
-      <c r="M53" s="1">
+      <c r="O53" s="1">
         <v>52</v>
       </c>
-      <c r="N53" s="1">
+      <c r="P53" s="1">
         <v>56</v>
       </c>
-      <c r="O53" s="1">
-        <v>60</v>
-      </c>
-      <c r="P53" s="1">
+      <c r="Q53" s="1">
+        <v>60</v>
+      </c>
+      <c r="R53" s="1">
         <v>65</v>
       </c>
-      <c r="Q53" s="1">
-        <v>999</v>
-      </c>
-      <c r="R53" s="1"/>
-      <c r="S53" s="1"/>
+      <c r="S53" s="1">
+        <v>999</v>
+      </c>
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
@@ -3793,34 +3737,32 @@
       <c r="I54" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J54" s="1"/>
-      <c r="K54"/>
-      <c r="L54">
+      <c r="L54" s="1"/>
+      <c r="M54"/>
+      <c r="N54">
         <v>48</v>
       </c>
-      <c r="M54" s="1">
+      <c r="O54" s="1">
         <v>52</v>
       </c>
-      <c r="N54" s="1">
+      <c r="P54" s="1">
         <v>56</v>
       </c>
-      <c r="O54" s="1">
-        <v>60</v>
-      </c>
-      <c r="P54" s="1">
+      <c r="Q54" s="1">
+        <v>60</v>
+      </c>
+      <c r="R54" s="1">
         <v>65</v>
       </c>
-      <c r="Q54" s="1">
+      <c r="S54" s="1">
         <v>71</v>
       </c>
-      <c r="R54" s="1">
+      <c r="T54" s="1">
         <v>79</v>
       </c>
-      <c r="S54" s="1">
-        <v>999</v>
-      </c>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
+      <c r="U54" s="1">
+        <v>999</v>
+      </c>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
@@ -3851,35 +3793,33 @@
       <c r="I55" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55" s="1"/>
-      <c r="N55" s="1">
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55" s="1"/>
+      <c r="P55" s="1">
         <v>56</v>
       </c>
-      <c r="O55" s="1">
-        <v>60</v>
-      </c>
-      <c r="P55" s="1">
+      <c r="Q55" s="1">
+        <v>60</v>
+      </c>
+      <c r="R55" s="1">
         <v>65</v>
       </c>
-      <c r="Q55" s="1">
+      <c r="S55" s="1">
         <v>71</v>
       </c>
-      <c r="R55" s="1">
+      <c r="T55" s="1">
         <v>79</v>
       </c>
-      <c r="S55" s="1">
+      <c r="U55" s="1">
         <v>88</v>
       </c>
-      <c r="T55" s="1">
+      <c r="V55" s="1">
         <v>94</v>
       </c>
-      <c r="U55" s="1">
-        <v>999</v>
-      </c>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1"/>
+      <c r="W55" s="1">
+        <v>999</v>
+      </c>
       <c r="X55" s="1"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.2">
@@ -3909,36 +3849,34 @@
       <c r="I56" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
       <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
       <c r="N56" s="1"/>
-      <c r="O56" s="1">
-        <v>60</v>
-      </c>
-      <c r="P56" s="1">
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1">
+        <v>60</v>
+      </c>
+      <c r="R56" s="1">
         <v>65</v>
       </c>
-      <c r="Q56" s="1">
+      <c r="S56" s="1">
         <v>71</v>
       </c>
-      <c r="R56" s="1">
+      <c r="T56" s="1">
         <v>79</v>
       </c>
-      <c r="S56" s="1">
+      <c r="U56" s="1">
         <v>88</v>
       </c>
-      <c r="T56" s="1">
+      <c r="V56" s="1">
         <v>94</v>
       </c>
-      <c r="U56" s="1">
+      <c r="W56" s="1">
         <v>110</v>
       </c>
-      <c r="V56" s="1">
-        <v>999</v>
-      </c>
-      <c r="W56" s="1"/>
-      <c r="X56" s="1"/>
+      <c r="X56" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
@@ -3967,36 +3905,34 @@
       <c r="I57" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
       <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
       <c r="N57" s="1"/>
-      <c r="O57" s="1">
-        <v>60</v>
-      </c>
-      <c r="P57" s="1">
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1">
+        <v>60</v>
+      </c>
+      <c r="R57" s="1">
         <v>65</v>
       </c>
-      <c r="Q57" s="1">
+      <c r="S57" s="1">
         <v>71</v>
       </c>
-      <c r="R57" s="1">
+      <c r="T57" s="1">
         <v>79</v>
       </c>
-      <c r="S57" s="1">
+      <c r="U57" s="1">
         <v>88</v>
       </c>
-      <c r="T57" s="1">
+      <c r="V57" s="1">
         <v>94</v>
       </c>
-      <c r="U57" s="1">
+      <c r="W57" s="1">
         <v>110</v>
       </c>
-      <c r="V57" s="1">
-        <v>999</v>
-      </c>
-      <c r="W57" s="1"/>
-      <c r="X57" s="1"/>
+      <c r="X57" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
@@ -4024,36 +3960,34 @@
       <c r="I58" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J58"/>
-      <c r="K58"/>
-      <c r="L58" s="1"/>
+      <c r="L58"/>
+      <c r="M58"/>
       <c r="N58" s="1"/>
-      <c r="O58" s="1">
-        <v>60</v>
-      </c>
-      <c r="P58" s="1">
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1">
+        <v>60</v>
+      </c>
+      <c r="R58" s="1">
         <v>65</v>
       </c>
-      <c r="Q58" s="1">
+      <c r="S58" s="1">
         <v>71</v>
       </c>
-      <c r="R58" s="1">
+      <c r="T58" s="1">
         <v>79</v>
       </c>
-      <c r="S58" s="1">
+      <c r="U58" s="1">
         <v>88</v>
       </c>
-      <c r="T58" s="1">
+      <c r="V58" s="1">
         <v>94</v>
       </c>
-      <c r="U58" s="1">
+      <c r="W58" s="1">
         <v>110</v>
       </c>
-      <c r="V58" s="1">
-        <v>999</v>
-      </c>
-      <c r="W58" s="1"/>
-      <c r="X58" s="1"/>
+      <c r="X58" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
@@ -4082,36 +4016,34 @@
       <c r="I59" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
       <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
       <c r="N59" s="1"/>
-      <c r="O59" s="1">
-        <v>60</v>
-      </c>
-      <c r="P59" s="1">
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1">
+        <v>60</v>
+      </c>
+      <c r="R59" s="1">
         <v>65</v>
       </c>
-      <c r="Q59" s="1">
+      <c r="S59" s="1">
         <v>71</v>
       </c>
-      <c r="R59" s="1">
+      <c r="T59" s="1">
         <v>79</v>
       </c>
-      <c r="S59" s="1">
+      <c r="U59" s="1">
         <v>88</v>
       </c>
-      <c r="T59" s="1">
+      <c r="V59" s="1">
         <v>94</v>
       </c>
-      <c r="U59" s="1">
+      <c r="W59" s="1">
         <v>110</v>
       </c>
-      <c r="V59" s="1">
-        <v>999</v>
-      </c>
-      <c r="W59" s="1"/>
-      <c r="X59" s="1"/>
+      <c r="X59" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
@@ -4140,36 +4072,34 @@
       <c r="I60" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
       <c r="N60" s="1"/>
-      <c r="O60" s="1">
-        <v>60</v>
-      </c>
-      <c r="P60" s="1">
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1">
+        <v>60</v>
+      </c>
+      <c r="R60" s="1">
         <v>65</v>
       </c>
-      <c r="Q60" s="1">
+      <c r="S60" s="1">
         <v>71</v>
       </c>
-      <c r="R60" s="1">
+      <c r="T60" s="1">
         <v>79</v>
       </c>
-      <c r="S60" s="1">
+      <c r="U60" s="1">
         <v>88</v>
       </c>
-      <c r="T60" s="1">
+      <c r="V60" s="1">
         <v>94</v>
       </c>
-      <c r="U60" s="1">
+      <c r="W60" s="1">
         <v>110</v>
       </c>
-      <c r="V60" s="1">
-        <v>999</v>
-      </c>
-      <c r="W60" s="1"/>
-      <c r="X60" s="1"/>
+      <c r="X60" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
@@ -4197,36 +4127,34 @@
       <c r="I61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J61"/>
-      <c r="K61"/>
-      <c r="L61" s="1"/>
+      <c r="L61"/>
+      <c r="M61"/>
       <c r="N61" s="1"/>
-      <c r="O61" s="1">
-        <v>60</v>
-      </c>
-      <c r="P61" s="1">
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1">
+        <v>60</v>
+      </c>
+      <c r="R61" s="1">
         <v>65</v>
       </c>
-      <c r="Q61" s="1">
+      <c r="S61" s="1">
         <v>71</v>
       </c>
-      <c r="R61" s="1">
+      <c r="T61" s="1">
         <v>79</v>
       </c>
-      <c r="S61" s="1">
+      <c r="U61" s="1">
         <v>88</v>
       </c>
-      <c r="T61" s="1">
+      <c r="V61" s="1">
         <v>94</v>
       </c>
-      <c r="U61" s="1">
+      <c r="W61" s="1">
         <v>110</v>
       </c>
-      <c r="V61" s="1">
-        <v>999</v>
-      </c>
-      <c r="W61" s="1"/>
-      <c r="X61" s="1"/>
+      <c r="X61" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
@@ -4254,36 +4182,34 @@
       <c r="I62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J62"/>
-      <c r="K62"/>
-      <c r="L62" s="1"/>
+      <c r="L62"/>
+      <c r="M62"/>
       <c r="N62" s="1"/>
-      <c r="O62" s="1">
-        <v>60</v>
-      </c>
-      <c r="P62" s="1">
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1">
+        <v>60</v>
+      </c>
+      <c r="R62" s="1">
         <v>65</v>
       </c>
-      <c r="Q62" s="1">
+      <c r="S62" s="1">
         <v>71</v>
       </c>
-      <c r="R62" s="1">
+      <c r="T62" s="1">
         <v>79</v>
       </c>
-      <c r="S62" s="1">
+      <c r="U62" s="1">
         <v>88</v>
       </c>
-      <c r="T62" s="1">
+      <c r="V62" s="1">
         <v>94</v>
       </c>
-      <c r="U62" s="1">
+      <c r="W62" s="1">
         <v>110</v>
       </c>
-      <c r="V62" s="1">
-        <v>999</v>
-      </c>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
+      <c r="X62" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
@@ -4312,36 +4238,34 @@
       <c r="I63" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
       <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
       <c r="N63" s="1"/>
-      <c r="O63" s="1">
-        <v>60</v>
-      </c>
-      <c r="P63" s="1">
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1">
+        <v>60</v>
+      </c>
+      <c r="R63" s="1">
         <v>65</v>
       </c>
-      <c r="Q63" s="1">
+      <c r="S63" s="1">
         <v>71</v>
       </c>
-      <c r="R63" s="1">
+      <c r="T63" s="1">
         <v>79</v>
       </c>
-      <c r="S63" s="1">
+      <c r="U63" s="1">
         <v>88</v>
       </c>
-      <c r="T63" s="1">
+      <c r="V63" s="1">
         <v>94</v>
       </c>
-      <c r="U63" s="1">
+      <c r="W63" s="1">
         <v>110</v>
       </c>
-      <c r="V63" s="1">
-        <v>999</v>
-      </c>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
+      <c r="X63" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
@@ -4369,36 +4293,34 @@
       <c r="I64" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64" s="1"/>
+      <c r="L64"/>
+      <c r="M64"/>
       <c r="N64" s="1"/>
-      <c r="O64" s="1">
-        <v>60</v>
-      </c>
-      <c r="P64" s="1">
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1">
+        <v>60</v>
+      </c>
+      <c r="R64" s="1">
         <v>65</v>
       </c>
-      <c r="Q64" s="1">
+      <c r="S64" s="1">
         <v>71</v>
       </c>
-      <c r="R64" s="1">
+      <c r="T64" s="1">
         <v>79</v>
       </c>
-      <c r="S64" s="1">
+      <c r="U64" s="1">
         <v>88</v>
       </c>
-      <c r="T64" s="1">
+      <c r="V64" s="1">
         <v>94</v>
       </c>
-      <c r="U64" s="1">
+      <c r="W64" s="1">
         <v>110</v>
       </c>
-      <c r="V64" s="1">
-        <v>999</v>
-      </c>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
+      <c r="X64" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
@@ -4426,36 +4348,34 @@
       <c r="I65" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J65"/>
-      <c r="K65"/>
-      <c r="L65" s="1"/>
+      <c r="L65"/>
+      <c r="M65"/>
       <c r="N65" s="1"/>
-      <c r="O65" s="1">
-        <v>60</v>
-      </c>
-      <c r="P65" s="1">
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1">
+        <v>60</v>
+      </c>
+      <c r="R65" s="1">
         <v>65</v>
       </c>
-      <c r="Q65" s="1">
+      <c r="S65" s="1">
         <v>71</v>
       </c>
-      <c r="R65" s="1">
+      <c r="T65" s="1">
         <v>79</v>
       </c>
-      <c r="S65" s="1">
+      <c r="U65" s="1">
         <v>88</v>
       </c>
-      <c r="T65" s="1">
+      <c r="V65" s="1">
         <v>94</v>
       </c>
-      <c r="U65" s="1">
+      <c r="W65" s="1">
         <v>110</v>
       </c>
-      <c r="V65" s="1">
-        <v>999</v>
-      </c>
-      <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
+      <c r="X65" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
@@ -4483,36 +4403,34 @@
       <c r="I66" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66" s="1"/>
+      <c r="L66"/>
+      <c r="M66"/>
       <c r="N66" s="1"/>
-      <c r="O66" s="1">
-        <v>60</v>
-      </c>
-      <c r="P66" s="1">
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1">
+        <v>60</v>
+      </c>
+      <c r="R66" s="1">
         <v>65</v>
       </c>
-      <c r="Q66" s="1">
+      <c r="S66" s="1">
         <v>71</v>
       </c>
-      <c r="R66" s="1">
+      <c r="T66" s="1">
         <v>79</v>
       </c>
-      <c r="S66" s="1">
+      <c r="U66" s="1">
         <v>88</v>
       </c>
-      <c r="T66" s="1">
+      <c r="V66" s="1">
         <v>94</v>
       </c>
-      <c r="U66" s="1">
+      <c r="W66" s="1">
         <v>110</v>
       </c>
-      <c r="V66" s="1">
-        <v>999</v>
-      </c>
-      <c r="W66" s="1"/>
-      <c r="X66" s="1"/>
+      <c r="X66" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
@@ -4540,36 +4458,34 @@
       <c r="I67" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67" s="1"/>
+      <c r="L67"/>
+      <c r="M67"/>
       <c r="N67" s="1"/>
-      <c r="O67" s="1">
-        <v>60</v>
-      </c>
-      <c r="P67" s="1">
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1">
+        <v>60</v>
+      </c>
+      <c r="R67" s="1">
         <v>65</v>
       </c>
-      <c r="Q67" s="1">
+      <c r="S67" s="1">
         <v>71</v>
       </c>
-      <c r="R67" s="1">
+      <c r="T67" s="1">
         <v>79</v>
       </c>
-      <c r="S67" s="1">
+      <c r="U67" s="1">
         <v>88</v>
       </c>
-      <c r="T67" s="1">
+      <c r="V67" s="1">
         <v>94</v>
       </c>
-      <c r="U67" s="1">
+      <c r="W67" s="1">
         <v>110</v>
       </c>
-      <c r="V67" s="1">
-        <v>999</v>
-      </c>
-      <c r="W67" s="1"/>
-      <c r="X67" s="1"/>
+      <c r="X67" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
@@ -4597,36 +4513,34 @@
       <c r="I68" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68" s="1"/>
+      <c r="L68"/>
+      <c r="M68"/>
       <c r="N68" s="1"/>
-      <c r="O68" s="1">
-        <v>60</v>
-      </c>
-      <c r="P68" s="1">
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1">
+        <v>60</v>
+      </c>
+      <c r="R68" s="1">
         <v>65</v>
       </c>
-      <c r="Q68" s="1">
+      <c r="S68" s="1">
         <v>71</v>
       </c>
-      <c r="R68" s="1">
+      <c r="T68" s="1">
         <v>79</v>
       </c>
-      <c r="S68" s="1">
+      <c r="U68" s="1">
         <v>88</v>
       </c>
-      <c r="T68" s="1">
+      <c r="V68" s="1">
         <v>94</v>
       </c>
-      <c r="U68" s="1">
+      <c r="W68" s="1">
         <v>110</v>
       </c>
-      <c r="V68" s="1">
-        <v>999</v>
-      </c>
-      <c r="W68" s="1"/>
-      <c r="X68" s="1"/>
+      <c r="X68" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
@@ -4654,36 +4568,34 @@
       <c r="I69" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J69"/>
-      <c r="K69"/>
-      <c r="L69" s="1"/>
+      <c r="L69"/>
+      <c r="M69"/>
       <c r="N69" s="1"/>
-      <c r="O69" s="1">
-        <v>60</v>
-      </c>
-      <c r="P69" s="1">
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1">
+        <v>60</v>
+      </c>
+      <c r="R69" s="1">
         <v>65</v>
       </c>
-      <c r="Q69" s="1">
+      <c r="S69" s="1">
         <v>71</v>
       </c>
-      <c r="R69" s="1">
+      <c r="T69" s="1">
         <v>79</v>
       </c>
-      <c r="S69" s="1">
+      <c r="U69" s="1">
         <v>88</v>
       </c>
-      <c r="T69" s="1">
+      <c r="V69" s="1">
         <v>94</v>
       </c>
-      <c r="U69" s="1">
+      <c r="W69" s="1">
         <v>110</v>
       </c>
-      <c r="V69" s="1">
-        <v>999</v>
-      </c>
-      <c r="W69" s="1"/>
-      <c r="X69" s="1"/>
+      <c r="X69" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
@@ -4711,36 +4623,34 @@
       <c r="I70" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J70"/>
-      <c r="K70"/>
-      <c r="L70" s="1"/>
+      <c r="L70"/>
+      <c r="M70"/>
       <c r="N70" s="1"/>
-      <c r="O70" s="1">
-        <v>60</v>
-      </c>
-      <c r="P70" s="1">
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1">
+        <v>60</v>
+      </c>
+      <c r="R70" s="1">
         <v>65</v>
       </c>
-      <c r="Q70" s="1">
+      <c r="S70" s="1">
         <v>71</v>
       </c>
-      <c r="R70" s="1">
+      <c r="T70" s="1">
         <v>79</v>
       </c>
-      <c r="S70" s="1">
+      <c r="U70" s="1">
         <v>88</v>
       </c>
-      <c r="T70" s="1">
+      <c r="V70" s="1">
         <v>94</v>
       </c>
-      <c r="U70" s="1">
+      <c r="W70" s="1">
         <v>110</v>
       </c>
-      <c r="V70" s="1">
-        <v>999</v>
-      </c>
-      <c r="W70" s="1"/>
-      <c r="X70" s="1"/>
+      <c r="X70" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
@@ -4768,36 +4678,34 @@
       <c r="I71" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J71"/>
-      <c r="K71"/>
-      <c r="L71" s="1"/>
+      <c r="L71"/>
+      <c r="M71"/>
       <c r="N71" s="1"/>
-      <c r="O71" s="1">
-        <v>60</v>
-      </c>
-      <c r="P71" s="1">
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1">
+        <v>60</v>
+      </c>
+      <c r="R71" s="1">
         <v>65</v>
       </c>
-      <c r="Q71" s="1">
+      <c r="S71" s="1">
         <v>71</v>
       </c>
-      <c r="R71" s="1">
+      <c r="T71" s="1">
         <v>79</v>
       </c>
-      <c r="S71" s="1">
+      <c r="U71" s="1">
         <v>88</v>
       </c>
-      <c r="T71" s="1">
+      <c r="V71" s="1">
         <v>94</v>
       </c>
-      <c r="U71" s="1">
+      <c r="W71" s="1">
         <v>110</v>
       </c>
-      <c r="V71" s="1">
-        <v>999</v>
-      </c>
-      <c r="W71" s="1"/>
-      <c r="X71" s="1"/>
+      <c r="X71" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
@@ -4825,36 +4733,34 @@
       <c r="I72" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72" s="1"/>
+      <c r="L72"/>
+      <c r="M72"/>
       <c r="N72" s="1"/>
-      <c r="O72" s="1">
-        <v>60</v>
-      </c>
-      <c r="P72" s="1">
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1">
+        <v>60</v>
+      </c>
+      <c r="R72" s="1">
         <v>65</v>
       </c>
-      <c r="Q72" s="1">
+      <c r="S72" s="1">
         <v>71</v>
       </c>
-      <c r="R72" s="1">
+      <c r="T72" s="1">
         <v>79</v>
       </c>
-      <c r="S72" s="1">
+      <c r="U72" s="1">
         <v>88</v>
       </c>
-      <c r="T72" s="1">
+      <c r="V72" s="1">
         <v>94</v>
       </c>
-      <c r="U72" s="1">
+      <c r="W72" s="1">
         <v>110</v>
       </c>
-      <c r="V72" s="1">
-        <v>999</v>
-      </c>
-      <c r="W72" s="1"/>
-      <c r="X72" s="1"/>
+      <c r="X72" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -4882,36 +4788,34 @@
       <c r="I73" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J73"/>
-      <c r="K73"/>
-      <c r="L73" s="1"/>
+      <c r="L73"/>
+      <c r="M73"/>
       <c r="N73" s="1"/>
-      <c r="O73" s="1">
-        <v>60</v>
-      </c>
-      <c r="P73" s="1">
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1">
+        <v>60</v>
+      </c>
+      <c r="R73" s="1">
         <v>65</v>
       </c>
-      <c r="Q73" s="1">
+      <c r="S73" s="1">
         <v>71</v>
       </c>
-      <c r="R73" s="1">
+      <c r="T73" s="1">
         <v>79</v>
       </c>
-      <c r="S73" s="1">
+      <c r="U73" s="1">
         <v>88</v>
       </c>
-      <c r="T73" s="1">
+      <c r="V73" s="1">
         <v>94</v>
       </c>
-      <c r="U73" s="1">
+      <c r="W73" s="1">
         <v>110</v>
       </c>
-      <c r="V73" s="1">
-        <v>999</v>
-      </c>
-      <c r="W73" s="1"/>
-      <c r="X73" s="1"/>
+      <c r="X73" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
@@ -4939,36 +4843,34 @@
       <c r="I74" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J74"/>
-      <c r="K74"/>
-      <c r="L74" s="1"/>
+      <c r="L74"/>
+      <c r="M74"/>
       <c r="N74" s="1"/>
-      <c r="O74" s="1">
-        <v>60</v>
-      </c>
-      <c r="P74" s="1">
+      <c r="P74" s="1"/>
+      <c r="Q74" s="1">
+        <v>60</v>
+      </c>
+      <c r="R74" s="1">
         <v>65</v>
       </c>
-      <c r="Q74" s="1">
+      <c r="S74" s="1">
         <v>71</v>
       </c>
-      <c r="R74" s="1">
+      <c r="T74" s="1">
         <v>79</v>
       </c>
-      <c r="S74" s="1">
+      <c r="U74" s="1">
         <v>88</v>
       </c>
-      <c r="T74" s="1">
+      <c r="V74" s="1">
         <v>94</v>
       </c>
-      <c r="U74" s="1">
+      <c r="W74" s="1">
         <v>110</v>
       </c>
-      <c r="V74" s="1">
-        <v>999</v>
-      </c>
-      <c r="W74" s="1"/>
-      <c r="X74" s="1"/>
+      <c r="X74" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
@@ -4996,36 +4898,34 @@
       <c r="I75" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J75"/>
-      <c r="K75"/>
-      <c r="L75" s="1"/>
+      <c r="L75"/>
+      <c r="M75"/>
       <c r="N75" s="1"/>
-      <c r="O75" s="1">
-        <v>60</v>
-      </c>
-      <c r="P75" s="1">
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1">
+        <v>60</v>
+      </c>
+      <c r="R75" s="1">
         <v>65</v>
       </c>
-      <c r="Q75" s="1">
+      <c r="S75" s="1">
         <v>71</v>
       </c>
-      <c r="R75" s="1">
+      <c r="T75" s="1">
         <v>79</v>
       </c>
-      <c r="S75" s="1">
+      <c r="U75" s="1">
         <v>88</v>
       </c>
-      <c r="T75" s="1">
+      <c r="V75" s="1">
         <v>94</v>
       </c>
-      <c r="U75" s="1">
+      <c r="W75" s="1">
         <v>110</v>
       </c>
-      <c r="V75" s="1">
-        <v>999</v>
-      </c>
-      <c r="W75" s="1"/>
-      <c r="X75" s="1"/>
+      <c r="X75" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
@@ -5053,36 +4953,34 @@
       <c r="I76" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J76"/>
-      <c r="K76"/>
-      <c r="L76" s="1"/>
+      <c r="L76"/>
+      <c r="M76"/>
       <c r="N76" s="1"/>
-      <c r="O76" s="1">
-        <v>60</v>
-      </c>
-      <c r="P76" s="1">
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1">
+        <v>60</v>
+      </c>
+      <c r="R76" s="1">
         <v>65</v>
       </c>
-      <c r="Q76" s="1">
+      <c r="S76" s="1">
         <v>71</v>
       </c>
-      <c r="R76" s="1">
+      <c r="T76" s="1">
         <v>79</v>
       </c>
-      <c r="S76" s="1">
+      <c r="U76" s="1">
         <v>88</v>
       </c>
-      <c r="T76" s="1">
+      <c r="V76" s="1">
         <v>94</v>
       </c>
-      <c r="U76" s="1">
+      <c r="W76" s="1">
         <v>110</v>
       </c>
-      <c r="V76" s="1">
-        <v>999</v>
-      </c>
-      <c r="W76" s="1"/>
-      <c r="X76" s="1"/>
+      <c r="X76" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
@@ -5110,36 +5008,34 @@
       <c r="I77" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J77"/>
-      <c r="K77"/>
-      <c r="L77" s="1"/>
+      <c r="L77"/>
+      <c r="M77"/>
       <c r="N77" s="1"/>
-      <c r="O77" s="1">
-        <v>60</v>
-      </c>
-      <c r="P77" s="1">
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1">
+        <v>60</v>
+      </c>
+      <c r="R77" s="1">
         <v>65</v>
       </c>
-      <c r="Q77" s="1">
+      <c r="S77" s="1">
         <v>71</v>
       </c>
-      <c r="R77" s="1">
+      <c r="T77" s="1">
         <v>79</v>
       </c>
-      <c r="S77" s="1">
+      <c r="U77" s="1">
         <v>88</v>
       </c>
-      <c r="T77" s="1">
+      <c r="V77" s="1">
         <v>94</v>
       </c>
-      <c r="U77" s="1">
+      <c r="W77" s="1">
         <v>110</v>
       </c>
-      <c r="V77" s="1">
-        <v>999</v>
-      </c>
-      <c r="W77" s="1"/>
-      <c r="X77" s="1"/>
+      <c r="X77" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
@@ -5167,36 +5063,34 @@
       <c r="I78" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J78"/>
-      <c r="K78"/>
-      <c r="L78" s="1"/>
+      <c r="L78"/>
+      <c r="M78"/>
       <c r="N78" s="1"/>
-      <c r="O78" s="1">
-        <v>60</v>
-      </c>
-      <c r="P78" s="1">
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1">
+        <v>60</v>
+      </c>
+      <c r="R78" s="1">
         <v>65</v>
       </c>
-      <c r="Q78" s="1">
+      <c r="S78" s="1">
         <v>71</v>
       </c>
-      <c r="R78" s="1">
+      <c r="T78" s="1">
         <v>79</v>
       </c>
-      <c r="S78" s="1">
+      <c r="U78" s="1">
         <v>88</v>
       </c>
-      <c r="T78" s="1">
+      <c r="V78" s="1">
         <v>94</v>
       </c>
-      <c r="U78" s="1">
+      <c r="W78" s="1">
         <v>110</v>
       </c>
-      <c r="V78" s="1">
-        <v>999</v>
-      </c>
-      <c r="W78" s="1"/>
-      <c r="X78" s="1"/>
+      <c r="X78" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
@@ -5224,36 +5118,34 @@
       <c r="I79" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J79"/>
-      <c r="K79"/>
-      <c r="L79" s="1"/>
+      <c r="L79"/>
+      <c r="M79"/>
       <c r="N79" s="1"/>
-      <c r="O79" s="1">
-        <v>60</v>
-      </c>
-      <c r="P79" s="1">
+      <c r="P79" s="1"/>
+      <c r="Q79" s="1">
+        <v>60</v>
+      </c>
+      <c r="R79" s="1">
         <v>65</v>
       </c>
-      <c r="Q79" s="1">
+      <c r="S79" s="1">
         <v>71</v>
       </c>
-      <c r="R79" s="1">
+      <c r="T79" s="1">
         <v>79</v>
       </c>
-      <c r="S79" s="1">
+      <c r="U79" s="1">
         <v>88</v>
       </c>
-      <c r="T79" s="1">
+      <c r="V79" s="1">
         <v>94</v>
       </c>
-      <c r="U79" s="1">
+      <c r="W79" s="1">
         <v>110</v>
       </c>
-      <c r="V79" s="1">
-        <v>999</v>
-      </c>
-      <c r="W79" s="1"/>
-      <c r="X79" s="1"/>
+      <c r="X79" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
@@ -5281,36 +5173,34 @@
       <c r="I80" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J80"/>
-      <c r="K80"/>
-      <c r="L80" s="1"/>
+      <c r="L80"/>
+      <c r="M80"/>
       <c r="N80" s="1"/>
-      <c r="O80" s="1">
-        <v>60</v>
-      </c>
-      <c r="P80" s="1">
+      <c r="P80" s="1"/>
+      <c r="Q80" s="1">
+        <v>60</v>
+      </c>
+      <c r="R80" s="1">
         <v>65</v>
       </c>
-      <c r="Q80" s="1">
+      <c r="S80" s="1">
         <v>71</v>
       </c>
-      <c r="R80" s="1">
+      <c r="T80" s="1">
         <v>79</v>
       </c>
-      <c r="S80" s="1">
+      <c r="U80" s="1">
         <v>88</v>
       </c>
-      <c r="T80" s="1">
+      <c r="V80" s="1">
         <v>94</v>
       </c>
-      <c r="U80" s="1">
+      <c r="W80" s="1">
         <v>110</v>
       </c>
-      <c r="V80" s="1">
-        <v>999</v>
-      </c>
-      <c r="W80" s="1"/>
-      <c r="X80" s="1"/>
+      <c r="X80" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
@@ -5338,36 +5228,34 @@
       <c r="I81" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J81"/>
-      <c r="K81"/>
-      <c r="L81" s="1"/>
+      <c r="L81"/>
+      <c r="M81"/>
       <c r="N81" s="1"/>
-      <c r="O81" s="1">
-        <v>60</v>
-      </c>
-      <c r="P81" s="1">
+      <c r="P81" s="1"/>
+      <c r="Q81" s="1">
+        <v>60</v>
+      </c>
+      <c r="R81" s="1">
         <v>65</v>
       </c>
-      <c r="Q81" s="1">
+      <c r="S81" s="1">
         <v>71</v>
       </c>
-      <c r="R81" s="1">
+      <c r="T81" s="1">
         <v>79</v>
       </c>
-      <c r="S81" s="1">
+      <c r="U81" s="1">
         <v>88</v>
       </c>
-      <c r="T81" s="1">
+      <c r="V81" s="1">
         <v>94</v>
       </c>
-      <c r="U81" s="1">
+      <c r="W81" s="1">
         <v>110</v>
       </c>
-      <c r="V81" s="1">
-        <v>999</v>
-      </c>
-      <c r="W81" s="1"/>
-      <c r="X81" s="1"/>
+      <c r="X81" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
@@ -5395,36 +5283,34 @@
       <c r="I82" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J82"/>
-      <c r="K82"/>
-      <c r="L82" s="1"/>
+      <c r="L82"/>
+      <c r="M82"/>
       <c r="N82" s="1"/>
-      <c r="O82" s="1">
-        <v>60</v>
-      </c>
-      <c r="P82" s="1">
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1">
+        <v>60</v>
+      </c>
+      <c r="R82" s="1">
         <v>65</v>
       </c>
-      <c r="Q82" s="1">
+      <c r="S82" s="1">
         <v>71</v>
       </c>
-      <c r="R82" s="1">
+      <c r="T82" s="1">
         <v>79</v>
       </c>
-      <c r="S82" s="1">
+      <c r="U82" s="1">
         <v>88</v>
       </c>
-      <c r="T82" s="1">
+      <c r="V82" s="1">
         <v>94</v>
       </c>
-      <c r="U82" s="1">
+      <c r="W82" s="1">
         <v>110</v>
       </c>
-      <c r="V82" s="1">
-        <v>999</v>
-      </c>
-      <c r="W82" s="1"/>
-      <c r="X82" s="1"/>
+      <c r="X82" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
@@ -5452,36 +5338,34 @@
       <c r="I83" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J83"/>
-      <c r="K83"/>
-      <c r="L83" s="1"/>
+      <c r="L83"/>
+      <c r="M83"/>
       <c r="N83" s="1"/>
-      <c r="O83" s="1">
-        <v>60</v>
-      </c>
-      <c r="P83" s="1">
+      <c r="P83" s="1"/>
+      <c r="Q83" s="1">
+        <v>60</v>
+      </c>
+      <c r="R83" s="1">
         <v>65</v>
       </c>
-      <c r="Q83" s="1">
+      <c r="S83" s="1">
         <v>71</v>
       </c>
-      <c r="R83" s="1">
+      <c r="T83" s="1">
         <v>79</v>
       </c>
-      <c r="S83" s="1">
+      <c r="U83" s="1">
         <v>88</v>
       </c>
-      <c r="T83" s="1">
+      <c r="V83" s="1">
         <v>94</v>
       </c>
-      <c r="U83" s="1">
+      <c r="W83" s="1">
         <v>110</v>
       </c>
-      <c r="V83" s="1">
-        <v>999</v>
-      </c>
-      <c r="W83" s="1"/>
-      <c r="X83" s="1"/>
+      <c r="X83" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
@@ -5509,36 +5393,34 @@
       <c r="I84" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J84"/>
-      <c r="K84"/>
-      <c r="L84" s="1"/>
+      <c r="L84"/>
+      <c r="M84"/>
       <c r="N84" s="1"/>
-      <c r="O84" s="1">
-        <v>60</v>
-      </c>
-      <c r="P84" s="1">
+      <c r="P84" s="1"/>
+      <c r="Q84" s="1">
+        <v>60</v>
+      </c>
+      <c r="R84" s="1">
         <v>65</v>
       </c>
-      <c r="Q84" s="1">
+      <c r="S84" s="1">
         <v>71</v>
       </c>
-      <c r="R84" s="1">
+      <c r="T84" s="1">
         <v>79</v>
       </c>
-      <c r="S84" s="1">
+      <c r="U84" s="1">
         <v>88</v>
       </c>
-      <c r="T84" s="1">
+      <c r="V84" s="1">
         <v>94</v>
       </c>
-      <c r="U84" s="1">
+      <c r="W84" s="1">
         <v>110</v>
       </c>
-      <c r="V84" s="1">
-        <v>999</v>
-      </c>
-      <c r="W84" s="1"/>
-      <c r="X84" s="1"/>
+      <c r="X84" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
@@ -5566,36 +5448,34 @@
       <c r="I85" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J85"/>
-      <c r="K85"/>
-      <c r="L85" s="1"/>
+      <c r="L85"/>
+      <c r="M85"/>
       <c r="N85" s="1"/>
-      <c r="O85" s="1">
-        <v>60</v>
-      </c>
-      <c r="P85" s="1">
+      <c r="P85" s="1"/>
+      <c r="Q85" s="1">
+        <v>60</v>
+      </c>
+      <c r="R85" s="1">
         <v>65</v>
       </c>
-      <c r="Q85" s="1">
+      <c r="S85" s="1">
         <v>71</v>
       </c>
-      <c r="R85" s="1">
+      <c r="T85" s="1">
         <v>79</v>
       </c>
-      <c r="S85" s="1">
+      <c r="U85" s="1">
         <v>88</v>
       </c>
-      <c r="T85" s="1">
+      <c r="V85" s="1">
         <v>94</v>
       </c>
-      <c r="U85" s="1">
+      <c r="W85" s="1">
         <v>110</v>
       </c>
-      <c r="V85" s="1">
-        <v>999</v>
-      </c>
-      <c r="W85" s="1"/>
-      <c r="X85" s="1"/>
+      <c r="X85" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
@@ -5623,36 +5503,34 @@
       <c r="I86" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J86"/>
-      <c r="K86"/>
-      <c r="L86" s="1"/>
+      <c r="L86"/>
+      <c r="M86"/>
       <c r="N86" s="1"/>
-      <c r="O86" s="1">
-        <v>60</v>
-      </c>
-      <c r="P86" s="1">
+      <c r="P86" s="1"/>
+      <c r="Q86" s="1">
+        <v>60</v>
+      </c>
+      <c r="R86" s="1">
         <v>65</v>
       </c>
-      <c r="Q86" s="1">
+      <c r="S86" s="1">
         <v>71</v>
       </c>
-      <c r="R86" s="1">
+      <c r="T86" s="1">
         <v>79</v>
       </c>
-      <c r="S86" s="1">
+      <c r="U86" s="1">
         <v>88</v>
       </c>
-      <c r="T86" s="1">
+      <c r="V86" s="1">
         <v>94</v>
       </c>
-      <c r="U86" s="1">
+      <c r="W86" s="1">
         <v>110</v>
       </c>
-      <c r="V86" s="1">
-        <v>999</v>
-      </c>
-      <c r="W86" s="1"/>
-      <c r="X86" s="1"/>
+      <c r="X86" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
@@ -5680,36 +5558,34 @@
       <c r="I87" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J87"/>
-      <c r="K87"/>
-      <c r="L87" s="1"/>
+      <c r="L87"/>
+      <c r="M87"/>
       <c r="N87" s="1"/>
-      <c r="O87" s="1">
-        <v>60</v>
-      </c>
-      <c r="P87" s="1">
+      <c r="P87" s="1"/>
+      <c r="Q87" s="1">
+        <v>60</v>
+      </c>
+      <c r="R87" s="1">
         <v>65</v>
       </c>
-      <c r="Q87" s="1">
+      <c r="S87" s="1">
         <v>71</v>
       </c>
-      <c r="R87" s="1">
+      <c r="T87" s="1">
         <v>79</v>
       </c>
-      <c r="S87" s="1">
+      <c r="U87" s="1">
         <v>88</v>
       </c>
-      <c r="T87" s="1">
+      <c r="V87" s="1">
         <v>94</v>
       </c>
-      <c r="U87" s="1">
+      <c r="W87" s="1">
         <v>110</v>
       </c>
-      <c r="V87" s="1">
-        <v>999</v>
-      </c>
-      <c r="W87" s="1"/>
-      <c r="X87" s="1"/>
+      <c r="X87" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
@@ -5737,36 +5613,34 @@
       <c r="I88" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J88"/>
-      <c r="K88"/>
-      <c r="L88" s="1"/>
+      <c r="L88"/>
+      <c r="M88"/>
       <c r="N88" s="1"/>
-      <c r="O88" s="1">
-        <v>60</v>
-      </c>
-      <c r="P88" s="1">
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1">
+        <v>60</v>
+      </c>
+      <c r="R88" s="1">
         <v>65</v>
       </c>
-      <c r="Q88" s="1">
+      <c r="S88" s="1">
         <v>71</v>
       </c>
-      <c r="R88" s="1">
+      <c r="T88" s="1">
         <v>79</v>
       </c>
-      <c r="S88" s="1">
+      <c r="U88" s="1">
         <v>88</v>
       </c>
-      <c r="T88" s="1">
+      <c r="V88" s="1">
         <v>94</v>
       </c>
-      <c r="U88" s="1">
+      <c r="W88" s="1">
         <v>110</v>
       </c>
-      <c r="V88" s="1">
-        <v>999</v>
-      </c>
-      <c r="W88" s="1"/>
-      <c r="X88" s="1"/>
+      <c r="X88" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
@@ -5794,36 +5668,34 @@
       <c r="I89" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J89"/>
-      <c r="K89"/>
-      <c r="L89" s="1"/>
+      <c r="L89"/>
+      <c r="M89"/>
       <c r="N89" s="1"/>
-      <c r="O89" s="1">
-        <v>60</v>
-      </c>
-      <c r="P89" s="1">
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1">
+        <v>60</v>
+      </c>
+      <c r="R89" s="1">
         <v>65</v>
       </c>
-      <c r="Q89" s="1">
+      <c r="S89" s="1">
         <v>71</v>
       </c>
-      <c r="R89" s="1">
+      <c r="T89" s="1">
         <v>79</v>
       </c>
-      <c r="S89" s="1">
+      <c r="U89" s="1">
         <v>88</v>
       </c>
-      <c r="T89" s="1">
+      <c r="V89" s="1">
         <v>94</v>
       </c>
-      <c r="U89" s="1">
+      <c r="W89" s="1">
         <v>110</v>
       </c>
-      <c r="V89" s="1">
-        <v>999</v>
-      </c>
-      <c r="W89" s="1"/>
-      <c r="X89" s="1"/>
+      <c r="X89" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
@@ -5851,36 +5723,34 @@
       <c r="I90" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J90"/>
-      <c r="K90"/>
-      <c r="L90" s="1"/>
+      <c r="L90"/>
+      <c r="M90"/>
       <c r="N90" s="1"/>
-      <c r="O90" s="1">
-        <v>60</v>
-      </c>
-      <c r="P90" s="1">
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1">
+        <v>60</v>
+      </c>
+      <c r="R90" s="1">
         <v>65</v>
       </c>
-      <c r="Q90" s="1">
+      <c r="S90" s="1">
         <v>71</v>
       </c>
-      <c r="R90" s="1">
+      <c r="T90" s="1">
         <v>79</v>
       </c>
-      <c r="S90" s="1">
+      <c r="U90" s="1">
         <v>88</v>
       </c>
-      <c r="T90" s="1">
+      <c r="V90" s="1">
         <v>94</v>
       </c>
-      <c r="U90" s="1">
+      <c r="W90" s="1">
         <v>110</v>
       </c>
-      <c r="V90" s="1">
-        <v>999</v>
-      </c>
-      <c r="W90" s="1"/>
-      <c r="X90" s="1"/>
+      <c r="X90" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
@@ -5908,36 +5778,34 @@
       <c r="I91" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J91"/>
-      <c r="K91"/>
-      <c r="L91" s="1"/>
+      <c r="L91"/>
+      <c r="M91"/>
       <c r="N91" s="1"/>
-      <c r="O91" s="1">
-        <v>60</v>
-      </c>
-      <c r="P91" s="1">
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1">
+        <v>60</v>
+      </c>
+      <c r="R91" s="1">
         <v>65</v>
       </c>
-      <c r="Q91" s="1">
+      <c r="S91" s="1">
         <v>71</v>
       </c>
-      <c r="R91" s="1">
+      <c r="T91" s="1">
         <v>79</v>
       </c>
-      <c r="S91" s="1">
+      <c r="U91" s="1">
         <v>88</v>
       </c>
-      <c r="T91" s="1">
+      <c r="V91" s="1">
         <v>94</v>
       </c>
-      <c r="U91" s="1">
+      <c r="W91" s="1">
         <v>110</v>
       </c>
-      <c r="V91" s="1">
-        <v>999</v>
-      </c>
-      <c r="W91" s="1"/>
-      <c r="X91" s="1"/>
+      <c r="X91" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
@@ -5968,22 +5836,20 @@
       <c r="I92" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
       <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
       <c r="N92" s="1"/>
-      <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
-      <c r="V92" s="1">
-        <v>999</v>
-      </c>
+      <c r="V92" s="1"/>
       <c r="W92" s="1"/>
-      <c r="X92" s="1"/>
+      <c r="X92" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
@@ -6013,22 +5879,20 @@
       <c r="I93" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
       <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
       <c r="N93" s="1"/>
-      <c r="O93" s="1"/>
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
-      <c r="V93" s="1">
-        <v>999</v>
-      </c>
+      <c r="V93" s="1"/>
       <c r="W93" s="1"/>
-      <c r="X93" s="1"/>
+      <c r="X93" s="1">
+        <v>999</v>
+      </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>

--- a/local/agegroups/USAW.xlsx
+++ b/local/agegroups/USAW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B032E598-4019-594E-993D-2ECDA62DDEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA28017-6A7D-8D4B-A2E7-D822C834E1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AgeGroups" sheetId="1" r:id="rId1"/>
@@ -5423,6 +5423,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D632D4-A7F2-1446-BD59-BB7933F25245}">
   <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="21" max="21" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
@@ -5524,10 +5528,16 @@
         <v>122</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N2">
         <v>2</v>
+      </c>
+      <c r="O2">
+        <v>5</v>
+      </c>
+      <c r="P2">
+        <v>5</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" t="b">
@@ -5569,10 +5579,16 @@
         <v>122</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N3">
         <v>2</v>
+      </c>
+      <c r="O3">
+        <v>5</v>
+      </c>
+      <c r="P3">
+        <v>5</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" t="b">
@@ -5614,10 +5630,16 @@
         <v>122</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N4">
         <v>2</v>
+      </c>
+      <c r="O4">
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <v>5</v>
       </c>
       <c r="Q4" s="7"/>
       <c r="R4" t="b">
@@ -5659,11 +5681,17 @@
         <v>122</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N5">
         <v>2</v>
       </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
+      </c>
       <c r="Q5" s="7"/>
       <c r="R5" t="b">
         <v>0</v>
@@ -5704,11 +5732,17 @@
         <v>122</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N6">
         <v>2</v>
       </c>
+      <c r="O6">
+        <v>5</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
+      </c>
       <c r="Q6" s="7"/>
       <c r="R6" t="b">
         <v>0</v>
@@ -5749,10 +5783,16 @@
         <v>122</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N7">
         <v>2</v>
+      </c>
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
       </c>
       <c r="Q7" s="7"/>
       <c r="R7" t="b">
@@ -5791,10 +5831,16 @@
         <v>23</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N8">
         <v>2</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>5</v>
       </c>
       <c r="Q8" s="7"/>
       <c r="R8" t="b">
@@ -5833,10 +5879,16 @@
         <v>23</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N9">
         <v>2</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9">
+        <v>5</v>
       </c>
       <c r="Q9" s="7"/>
       <c r="R9" t="b">

--- a/local/agegroups/USAW.xlsx
+++ b/local/agegroups/USAW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246311FE-6F9C-3D49-B4A0-75E0BB97ECF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5D608C-8DB5-5D4D-9B2C-38A9561C465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36840" yWindow="3160" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4540,7 +4540,8 @@
         <v>11</v>
       </c>
       <c r="F69" s="5" t="b">
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G69" s="2">
         <v>32</v>
@@ -4596,8 +4597,8 @@
         <v>13</v>
       </c>
       <c r="F70" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G70" s="2">
         <v>32</v>
@@ -4653,8 +4654,8 @@
         <v>15</v>
       </c>
       <c r="F71" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71"/>
@@ -4707,8 +4708,8 @@
         <v>17</v>
       </c>
       <c r="F72" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H72"/>
       <c r="I72"/>
@@ -4809,8 +4810,8 @@
         <v>20</v>
       </c>
       <c r="F74" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H74"/>
       <c r="I74"/>
@@ -4860,8 +4861,8 @@
         <v>999</v>
       </c>
       <c r="F75" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H75"/>
       <c r="I75"/>
@@ -6691,7 +6692,8 @@
         <v>11</v>
       </c>
       <c r="F111" s="5" t="b">
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G111" s="2">
         <v>32</v>
@@ -6747,8 +6749,8 @@
         <v>13</v>
       </c>
       <c r="F112" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G112" s="2">
         <v>32</v>
@@ -6804,8 +6806,8 @@
         <v>15</v>
       </c>
       <c r="F113" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H113" s="1"/>
       <c r="I113"/>
@@ -6858,8 +6860,8 @@
         <v>17</v>
       </c>
       <c r="F114" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H114"/>
       <c r="I114"/>
@@ -6960,8 +6962,8 @@
         <v>20</v>
       </c>
       <c r="F116" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H116"/>
       <c r="I116"/>
@@ -7011,8 +7013,8 @@
         <v>999</v>
       </c>
       <c r="F117" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H117"/>
       <c r="I117"/>
@@ -8842,7 +8844,8 @@
         <v>11</v>
       </c>
       <c r="F153" s="5" t="b">
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G153" s="2">
         <v>32</v>
@@ -8898,8 +8901,8 @@
         <v>13</v>
       </c>
       <c r="F154" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G154" s="2">
         <v>32</v>
@@ -8955,8 +8958,8 @@
         <v>15</v>
       </c>
       <c r="F155" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155"/>
@@ -9009,8 +9012,8 @@
         <v>17</v>
       </c>
       <c r="F156" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H156"/>
       <c r="I156"/>
@@ -9111,8 +9114,8 @@
         <v>20</v>
       </c>
       <c r="F158" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H158"/>
       <c r="I158"/>
@@ -9162,8 +9165,8 @@
         <v>999</v>
       </c>
       <c r="F159" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H159"/>
       <c r="I159"/>
@@ -10993,7 +10996,8 @@
         <v>11</v>
       </c>
       <c r="F195" s="5" t="b">
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G195" s="2">
         <v>32</v>
@@ -11049,8 +11053,8 @@
         <v>13</v>
       </c>
       <c r="F196" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G196" s="2">
         <v>32</v>
@@ -11106,8 +11110,8 @@
         <v>15</v>
       </c>
       <c r="F197" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H197" s="1"/>
       <c r="I197"/>
@@ -11160,8 +11164,8 @@
         <v>17</v>
       </c>
       <c r="F198" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H198"/>
       <c r="I198"/>
@@ -11262,8 +11266,8 @@
         <v>20</v>
       </c>
       <c r="F200" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H200"/>
       <c r="I200"/>
@@ -11313,8 +11317,8 @@
         <v>999</v>
       </c>
       <c r="F201" s="5" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H201"/>
       <c r="I201"/>

--- a/local/agegroups/USAW.xlsx
+++ b/local/agegroups/USAW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5D608C-8DB5-5D4D-9B2C-38A9561C465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0605202-1E88-3A45-93A4-1013084632D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36840" yWindow="3160" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31320" yWindow="10160" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AgeGroups" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="239">
   <si>
     <t>code</t>
   </si>
@@ -286,9 +286,6 @@
   </si>
   <si>
     <t>DEFAULT</t>
-  </si>
-  <si>
-    <t>QPoints</t>
   </si>
   <si>
     <t>ADH U11</t>
@@ -3445,10 +3442,10 @@
     </row>
     <row r="48" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>7</v>
@@ -3501,10 +3498,10 @@
     </row>
     <row r="49" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>7</v>
@@ -3558,10 +3555,10 @@
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>7</v>
@@ -3611,10 +3608,10 @@
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>7</v>
@@ -3662,10 +3659,10 @@
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>7</v>
@@ -3711,10 +3708,10 @@
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>7</v>
@@ -3762,10 +3759,10 @@
     </row>
     <row r="54" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>7</v>
@@ -3811,10 +3808,10 @@
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>7</v>
@@ -3862,10 +3859,10 @@
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>7</v>
@@ -3913,10 +3910,10 @@
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>7</v>
@@ -3964,10 +3961,10 @@
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>7</v>
@@ -4015,10 +4012,10 @@
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>7</v>
@@ -4066,10 +4063,10 @@
     </row>
     <row r="60" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>7</v>
@@ -4117,10 +4114,10 @@
     </row>
     <row r="61" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>7</v>
@@ -4168,10 +4165,10 @@
     </row>
     <row r="62" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>7</v>
@@ -4219,10 +4216,10 @@
     </row>
     <row r="63" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>7</v>
@@ -4270,10 +4267,10 @@
     </row>
     <row r="64" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>7</v>
@@ -4321,10 +4318,10 @@
     </row>
     <row r="65" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>7</v>
@@ -4372,10 +4369,10 @@
     </row>
     <row r="66" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>7</v>
@@ -4423,10 +4420,10 @@
     </row>
     <row r="67" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>7</v>
@@ -4474,10 +4471,10 @@
     </row>
     <row r="68" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>7</v>
@@ -4525,10 +4522,10 @@
     </row>
     <row r="69" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>29</v>
@@ -4582,10 +4579,10 @@
     </row>
     <row r="70" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>29</v>
@@ -4639,10 +4636,10 @@
     </row>
     <row r="71" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>29</v>
@@ -4693,10 +4690,10 @@
     </row>
     <row r="72" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>29</v>
@@ -4744,10 +4741,10 @@
     </row>
     <row r="73" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>29</v>
@@ -4795,10 +4792,10 @@
     </row>
     <row r="74" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>29</v>
@@ -4846,10 +4843,10 @@
     </row>
     <row r="75" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>29</v>
@@ -4897,10 +4894,10 @@
     </row>
     <row r="76" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>29</v>
@@ -4947,10 +4944,10 @@
     </row>
     <row r="77" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>29</v>
@@ -4997,10 +4994,10 @@
     </row>
     <row r="78" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>29</v>
@@ -5047,10 +5044,10 @@
     </row>
     <row r="79" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>29</v>
@@ -5097,10 +5094,10 @@
     </row>
     <row r="80" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>29</v>
@@ -5147,10 +5144,10 @@
     </row>
     <row r="81" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>29</v>
@@ -5197,10 +5194,10 @@
     </row>
     <row r="82" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>29</v>
@@ -5247,10 +5244,10 @@
     </row>
     <row r="83" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>29</v>
@@ -5297,10 +5294,10 @@
     </row>
     <row r="84" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>29</v>
@@ -5347,10 +5344,10 @@
     </row>
     <row r="85" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>29</v>
@@ -5397,10 +5394,10 @@
     </row>
     <row r="86" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>29</v>
@@ -5447,10 +5444,10 @@
     </row>
     <row r="87" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>29</v>
@@ -5497,10 +5494,10 @@
     </row>
     <row r="88" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>29</v>
@@ -5547,10 +5544,10 @@
     </row>
     <row r="89" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>29</v>
@@ -5597,10 +5594,10 @@
     </row>
     <row r="90" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>7</v>
@@ -5653,10 +5650,10 @@
     </row>
     <row r="91" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>7</v>
@@ -5710,10 +5707,10 @@
     </row>
     <row r="92" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>7</v>
@@ -5763,10 +5760,10 @@
     </row>
     <row r="93" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>7</v>
@@ -5814,10 +5811,10 @@
     </row>
     <row r="94" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>7</v>
@@ -5863,10 +5860,10 @@
     </row>
     <row r="95" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>7</v>
@@ -5914,10 +5911,10 @@
     </row>
     <row r="96" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>7</v>
@@ -5963,10 +5960,10 @@
     </row>
     <row r="97" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>7</v>
@@ -6014,10 +6011,10 @@
     </row>
     <row r="98" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>7</v>
@@ -6065,10 +6062,10 @@
     </row>
     <row r="99" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>7</v>
@@ -6116,10 +6113,10 @@
     </row>
     <row r="100" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>7</v>
@@ -6167,10 +6164,10 @@
     </row>
     <row r="101" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>7</v>
@@ -6218,10 +6215,10 @@
     </row>
     <row r="102" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>7</v>
@@ -6269,10 +6266,10 @@
     </row>
     <row r="103" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>7</v>
@@ -6320,10 +6317,10 @@
     </row>
     <row r="104" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>7</v>
@@ -6371,10 +6368,10 @@
     </row>
     <row r="105" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>7</v>
@@ -6422,10 +6419,10 @@
     </row>
     <row r="106" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>7</v>
@@ -6473,10 +6470,10 @@
     </row>
     <row r="107" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>7</v>
@@ -6524,10 +6521,10 @@
     </row>
     <row r="108" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>7</v>
@@ -6575,10 +6572,10 @@
     </row>
     <row r="109" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>7</v>
@@ -6626,10 +6623,10 @@
     </row>
     <row r="110" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>7</v>
@@ -6677,10 +6674,10 @@
     </row>
     <row r="111" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>29</v>
@@ -6734,10 +6731,10 @@
     </row>
     <row r="112" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>29</v>
@@ -6791,10 +6788,10 @@
     </row>
     <row r="113" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>29</v>
@@ -6845,10 +6842,10 @@
     </row>
     <row r="114" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>29</v>
@@ -6896,10 +6893,10 @@
     </row>
     <row r="115" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>29</v>
@@ -6947,10 +6944,10 @@
     </row>
     <row r="116" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>29</v>
@@ -6998,10 +6995,10 @@
     </row>
     <row r="117" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>29</v>
@@ -7049,10 +7046,10 @@
     </row>
     <row r="118" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>29</v>
@@ -7099,10 +7096,10 @@
     </row>
     <row r="119" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>29</v>
@@ -7149,10 +7146,10 @@
     </row>
     <row r="120" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>29</v>
@@ -7199,10 +7196,10 @@
     </row>
     <row r="121" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>29</v>
@@ -7249,10 +7246,10 @@
     </row>
     <row r="122" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>29</v>
@@ -7299,10 +7296,10 @@
     </row>
     <row r="123" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>29</v>
@@ -7349,10 +7346,10 @@
     </row>
     <row r="124" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>29</v>
@@ -7399,10 +7396,10 @@
     </row>
     <row r="125" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>29</v>
@@ -7449,10 +7446,10 @@
     </row>
     <row r="126" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>29</v>
@@ -7499,10 +7496,10 @@
     </row>
     <row r="127" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>29</v>
@@ -7549,10 +7546,10 @@
     </row>
     <row r="128" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>29</v>
@@ -7599,10 +7596,10 @@
     </row>
     <row r="129" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>29</v>
@@ -7649,10 +7646,10 @@
     </row>
     <row r="130" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>29</v>
@@ -7699,10 +7696,10 @@
     </row>
     <row r="131" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>29</v>
@@ -7749,10 +7746,10 @@
     </row>
     <row r="132" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>7</v>
@@ -7805,10 +7802,10 @@
     </row>
     <row r="133" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>7</v>
@@ -7862,10 +7859,10 @@
     </row>
     <row r="134" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>7</v>
@@ -7915,10 +7912,10 @@
     </row>
     <row r="135" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>7</v>
@@ -7966,10 +7963,10 @@
     </row>
     <row r="136" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>7</v>
@@ -8015,10 +8012,10 @@
     </row>
     <row r="137" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>7</v>
@@ -8066,10 +8063,10 @@
     </row>
     <row r="138" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>7</v>
@@ -8115,10 +8112,10 @@
     </row>
     <row r="139" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>7</v>
@@ -8166,10 +8163,10 @@
     </row>
     <row r="140" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>7</v>
@@ -8217,10 +8214,10 @@
     </row>
     <row r="141" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>7</v>
@@ -8268,10 +8265,10 @@
     </row>
     <row r="142" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>7</v>
@@ -8319,10 +8316,10 @@
     </row>
     <row r="143" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>7</v>
@@ -8370,10 +8367,10 @@
     </row>
     <row r="144" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>7</v>
@@ -8421,10 +8418,10 @@
     </row>
     <row r="145" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>7</v>
@@ -8472,10 +8469,10 @@
     </row>
     <row r="146" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>7</v>
@@ -8523,10 +8520,10 @@
     </row>
     <row r="147" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>7</v>
@@ -8574,10 +8571,10 @@
     </row>
     <row r="148" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>7</v>
@@ -8625,10 +8622,10 @@
     </row>
     <row r="149" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>7</v>
@@ -8676,10 +8673,10 @@
     </row>
     <row r="150" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>7</v>
@@ -8727,10 +8724,10 @@
     </row>
     <row r="151" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>7</v>
@@ -8778,10 +8775,10 @@
     </row>
     <row r="152" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>7</v>
@@ -8829,10 +8826,10 @@
     </row>
     <row r="153" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>29</v>
@@ -8886,10 +8883,10 @@
     </row>
     <row r="154" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>29</v>
@@ -8943,10 +8940,10 @@
     </row>
     <row r="155" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>29</v>
@@ -8997,10 +8994,10 @@
     </row>
     <row r="156" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>29</v>
@@ -9048,10 +9045,10 @@
     </row>
     <row r="157" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>29</v>
@@ -9099,10 +9096,10 @@
     </row>
     <row r="158" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>29</v>
@@ -9150,10 +9147,10 @@
     </row>
     <row r="159" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>29</v>
@@ -9201,10 +9198,10 @@
     </row>
     <row r="160" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>29</v>
@@ -9251,10 +9248,10 @@
     </row>
     <row r="161" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>29</v>
@@ -9301,10 +9298,10 @@
     </row>
     <row r="162" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>29</v>
@@ -9351,10 +9348,10 @@
     </row>
     <row r="163" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>29</v>
@@ -9401,10 +9398,10 @@
     </row>
     <row r="164" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>29</v>
@@ -9451,10 +9448,10 @@
     </row>
     <row r="165" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>29</v>
@@ -9501,10 +9498,10 @@
     </row>
     <row r="166" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>29</v>
@@ -9551,10 +9548,10 @@
     </row>
     <row r="167" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>29</v>
@@ -9601,10 +9598,10 @@
     </row>
     <row r="168" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>29</v>
@@ -9651,10 +9648,10 @@
     </row>
     <row r="169" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A169" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>29</v>
@@ -9701,10 +9698,10 @@
     </row>
     <row r="170" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A170" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>29</v>
@@ -9751,10 +9748,10 @@
     </row>
     <row r="171" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A171" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>29</v>
@@ -9801,10 +9798,10 @@
     </row>
     <row r="172" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A172" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>29</v>
@@ -9851,10 +9848,10 @@
     </row>
     <row r="173" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A173" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>29</v>
@@ -9901,10 +9898,10 @@
     </row>
     <row r="174" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>7</v>
@@ -9957,10 +9954,10 @@
     </row>
     <row r="175" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>7</v>
@@ -10014,10 +10011,10 @@
     </row>
     <row r="176" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>7</v>
@@ -10067,10 +10064,10 @@
     </row>
     <row r="177" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>7</v>
@@ -10118,10 +10115,10 @@
     </row>
     <row r="178" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>7</v>
@@ -10167,10 +10164,10 @@
     </row>
     <row r="179" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>7</v>
@@ -10218,10 +10215,10 @@
     </row>
     <row r="180" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>7</v>
@@ -10267,10 +10264,10 @@
     </row>
     <row r="181" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>7</v>
@@ -10318,10 +10315,10 @@
     </row>
     <row r="182" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>7</v>
@@ -10369,10 +10366,10 @@
     </row>
     <row r="183" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>7</v>
@@ -10420,10 +10417,10 @@
     </row>
     <row r="184" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>7</v>
@@ -10471,10 +10468,10 @@
     </row>
     <row r="185" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>7</v>
@@ -10522,10 +10519,10 @@
     </row>
     <row r="186" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>7</v>
@@ -10573,10 +10570,10 @@
     </row>
     <row r="187" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>7</v>
@@ -10624,10 +10621,10 @@
     </row>
     <row r="188" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>7</v>
@@ -10675,10 +10672,10 @@
     </row>
     <row r="189" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>7</v>
@@ -10726,10 +10723,10 @@
     </row>
     <row r="190" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>7</v>
@@ -10777,10 +10774,10 @@
     </row>
     <row r="191" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>7</v>
@@ -10828,10 +10825,10 @@
     </row>
     <row r="192" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>7</v>
@@ -10879,10 +10876,10 @@
     </row>
     <row r="193" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>7</v>
@@ -10930,10 +10927,10 @@
     </row>
     <row r="194" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>7</v>
@@ -10981,10 +10978,10 @@
     </row>
     <row r="195" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>29</v>
@@ -11038,10 +11035,10 @@
     </row>
     <row r="196" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>29</v>
@@ -11095,10 +11092,10 @@
     </row>
     <row r="197" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>29</v>
@@ -11149,10 +11146,10 @@
     </row>
     <row r="198" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>29</v>
@@ -11200,10 +11197,10 @@
     </row>
     <row r="199" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>29</v>
@@ -11251,10 +11248,10 @@
     </row>
     <row r="200" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>29</v>
@@ -11302,10 +11299,10 @@
     </row>
     <row r="201" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>29</v>
@@ -11353,10 +11350,10 @@
     </row>
     <row r="202" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>29</v>
@@ -11403,10 +11400,10 @@
     </row>
     <row r="203" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>29</v>
@@ -11453,10 +11450,10 @@
     </row>
     <row r="204" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>29</v>
@@ -11503,10 +11500,10 @@
     </row>
     <row r="205" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>29</v>
@@ -11553,10 +11550,10 @@
     </row>
     <row r="206" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>29</v>
@@ -11603,10 +11600,10 @@
     </row>
     <row r="207" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>29</v>
@@ -11653,10 +11650,10 @@
     </row>
     <row r="208" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>29</v>
@@ -11703,10 +11700,10 @@
     </row>
     <row r="209" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>29</v>
@@ -11753,10 +11750,10 @@
     </row>
     <row r="210" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>29</v>
@@ -11803,10 +11800,10 @@
     </row>
     <row r="211" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A211" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>29</v>
@@ -11853,10 +11850,10 @@
     </row>
     <row r="212" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A212" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>29</v>
@@ -11903,10 +11900,10 @@
     </row>
     <row r="213" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>29</v>
@@ -11953,10 +11950,10 @@
     </row>
     <row r="214" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A214" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>29</v>
@@ -12003,10 +12000,10 @@
     </row>
     <row r="215" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A215" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>29</v>
@@ -12221,8 +12218,8 @@
       <c r="E3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>83</v>
+      <c r="F3" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="I3">
         <v>28</v>
@@ -12360,7 +12357,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>6</v>
@@ -12411,7 +12408,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>13</v>
@@ -12462,7 +12459,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>6</v>
@@ -12513,7 +12510,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>13</v>
@@ -12564,7 +12561,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>6</v>
@@ -12615,7 +12612,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>13</v>
@@ -12666,7 +12663,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>6</v>
@@ -12717,7 +12714,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>13</v>
